--- a/product_selector_out/STM32WL5x-Ex.xlsx
+++ b/product_selector_out/STM32WL5x-Ex.xlsx
@@ -61,12 +61,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFEB9C"/>
+        <fgColor rgb="00F2F2F2"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00F2F2F2"/>
+        <fgColor rgb="00FFEB9C"/>
       </patternFill>
     </fill>
     <fill>
@@ -1350,7 +1350,7 @@
       </c>
       <c r="BP12" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32wl55cc.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -1692,7 +1692,7 @@
       </c>
       <c r="BP13" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32wle5c8.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -2034,7 +2034,7 @@
       </c>
       <c r="BP14" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32wle5c8.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -2376,7 +2376,7 @@
       </c>
       <c r="BP15" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32wl55cc.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -2718,7 +2718,7 @@
       </c>
       <c r="BP16" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32wle5c8.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -3060,7 +3060,7 @@
       </c>
       <c r="BP17" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32wle5c8.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -3402,7 +3402,7 @@
       </c>
       <c r="BP18" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32wl55cc.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -4086,7 +4086,7 @@
       </c>
       <c r="BP20" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32wle5c8.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -4428,7 +4428,7 @@
       </c>
       <c r="BP21" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32wle5c8.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -4770,7 +4770,7 @@
       </c>
       <c r="BP22" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32wle5c8.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -5112,7 +5112,7 @@
       </c>
       <c r="BP23" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32wle5c8.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -5454,7 +5454,7 @@
       </c>
       <c r="BP24" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32wle5c8.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -5796,7 +5796,7 @@
       </c>
       <c r="BP25" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32wle5c8.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -6138,7 +6138,7 @@
       </c>
       <c r="BP26" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32wle5c8.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -7122,9 +7122,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E12" s="7" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="E12" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F12" s="6" t="inlineStr">
@@ -7132,7 +7132,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="G12" s="8" t="inlineStr">
+      <c r="G12" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -7147,7 +7147,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="J12" s="8" t="inlineStr">
+      <c r="J12" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -7162,7 +7162,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="M12" s="8" t="inlineStr">
+      <c r="M12" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -7172,17 +7172,17 @@
           <t>API</t>
         </is>
       </c>
-      <c r="O12" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="P12" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Q12" s="8" t="inlineStr">
+      <c r="O12" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="P12" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Q12" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -7212,22 +7212,22 @@
           <t>API</t>
         </is>
       </c>
-      <c r="W12" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="X12" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Y12" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Z12" s="8" t="inlineStr">
+      <c r="W12" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="X12" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Y12" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Z12" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -7247,22 +7247,22 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AD12" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AE12" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AF12" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AG12" s="8" t="inlineStr">
+      <c r="AD12" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AE12" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AF12" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AG12" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -7272,7 +7272,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AI12" s="8" t="inlineStr">
+      <c r="AI12" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -7297,17 +7297,17 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AN12" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AO12" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AP12" s="8" t="inlineStr">
+      <c r="AN12" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AO12" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AP12" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -7322,7 +7322,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AS12" s="8" t="inlineStr">
+      <c r="AS12" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -7332,12 +7332,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AU12" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AV12" s="8" t="inlineStr">
+      <c r="AU12" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AV12" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -7347,14 +7347,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AX12" s="7" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AY12" s="9" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AX12" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AY12" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AZ12" s="6" t="inlineStr">
@@ -7417,12 +7417,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BL12" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BM12" s="8" t="inlineStr">
+      <c r="BL12" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BM12" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -7437,9 +7437,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BP12" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BP12" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -7464,9 +7464,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E13" s="9" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="E13" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F13" s="6" t="inlineStr">
@@ -7474,22 +7474,22 @@
           <t>API</t>
         </is>
       </c>
-      <c r="G13" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="H13" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="I13" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="J13" s="8" t="inlineStr">
+      <c r="G13" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="H13" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="I13" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="J13" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -7504,7 +7504,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="M13" s="8" t="inlineStr">
+      <c r="M13" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -7514,17 +7514,17 @@
           <t>API</t>
         </is>
       </c>
-      <c r="O13" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="P13" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Q13" s="8" t="inlineStr">
+      <c r="O13" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="P13" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Q13" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -7554,22 +7554,22 @@
           <t>API</t>
         </is>
       </c>
-      <c r="W13" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="X13" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Y13" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Z13" s="8" t="inlineStr">
+      <c r="W13" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="X13" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Y13" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Z13" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -7589,22 +7589,22 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AD13" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AE13" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AF13" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AG13" s="8" t="inlineStr">
+      <c r="AD13" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AE13" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AF13" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AG13" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -7614,7 +7614,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AI13" s="8" t="inlineStr">
+      <c r="AI13" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -7639,17 +7639,17 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AN13" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AO13" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AP13" s="8" t="inlineStr">
+      <c r="AN13" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AO13" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AP13" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -7664,7 +7664,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AS13" s="8" t="inlineStr">
+      <c r="AS13" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -7674,12 +7674,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AU13" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AV13" s="8" t="inlineStr">
+      <c r="AU13" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AV13" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -7689,14 +7689,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AX13" s="7" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AY13" s="9" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AX13" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AY13" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AZ13" s="6" t="inlineStr">
@@ -7759,12 +7759,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BL13" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BM13" s="8" t="inlineStr">
+      <c r="BL13" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BM13" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -7779,9 +7779,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BP13" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BP13" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -7806,9 +7806,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E14" s="9" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="E14" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F14" s="6" t="inlineStr">
@@ -7816,22 +7816,22 @@
           <t>API</t>
         </is>
       </c>
-      <c r="G14" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="H14" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="I14" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="J14" s="8" t="inlineStr">
+      <c r="G14" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="H14" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="I14" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="J14" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -7846,7 +7846,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="M14" s="8" t="inlineStr">
+      <c r="M14" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -7856,17 +7856,17 @@
           <t>API</t>
         </is>
       </c>
-      <c r="O14" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="P14" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Q14" s="8" t="inlineStr">
+      <c r="O14" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="P14" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Q14" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -7896,22 +7896,22 @@
           <t>API</t>
         </is>
       </c>
-      <c r="W14" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="X14" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Y14" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Z14" s="8" t="inlineStr">
+      <c r="W14" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="X14" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Y14" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Z14" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -7931,22 +7931,22 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AD14" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AE14" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AF14" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AG14" s="8" t="inlineStr">
+      <c r="AD14" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AE14" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AF14" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AG14" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -7956,7 +7956,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AI14" s="8" t="inlineStr">
+      <c r="AI14" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -7981,17 +7981,17 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AN14" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AO14" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AP14" s="8" t="inlineStr">
+      <c r="AN14" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AO14" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AP14" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -8006,7 +8006,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AS14" s="8" t="inlineStr">
+      <c r="AS14" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -8016,12 +8016,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AU14" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AV14" s="8" t="inlineStr">
+      <c r="AU14" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AV14" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -8031,14 +8031,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AX14" s="7" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AY14" s="9" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AX14" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AY14" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AZ14" s="6" t="inlineStr">
@@ -8101,12 +8101,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BL14" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BM14" s="8" t="inlineStr">
+      <c r="BL14" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BM14" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -8121,9 +8121,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BP14" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BP14" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -8148,9 +8148,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E15" s="7" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="E15" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F15" s="6" t="inlineStr">
@@ -8158,7 +8158,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="G15" s="8" t="inlineStr">
+      <c r="G15" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -8173,7 +8173,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="J15" s="8" t="inlineStr">
+      <c r="J15" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -8188,7 +8188,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="M15" s="8" t="inlineStr">
+      <c r="M15" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -8198,17 +8198,17 @@
           <t>API</t>
         </is>
       </c>
-      <c r="O15" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="P15" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Q15" s="8" t="inlineStr">
+      <c r="O15" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="P15" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Q15" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -8238,22 +8238,22 @@
           <t>API</t>
         </is>
       </c>
-      <c r="W15" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="X15" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Y15" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Z15" s="8" t="inlineStr">
+      <c r="W15" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="X15" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Y15" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Z15" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -8273,22 +8273,22 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AD15" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AE15" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AF15" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AG15" s="8" t="inlineStr">
+      <c r="AD15" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AE15" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AF15" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AG15" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -8298,7 +8298,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AI15" s="8" t="inlineStr">
+      <c r="AI15" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -8323,17 +8323,17 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AN15" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AO15" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AP15" s="8" t="inlineStr">
+      <c r="AN15" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AO15" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AP15" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -8348,7 +8348,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AS15" s="8" t="inlineStr">
+      <c r="AS15" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -8358,12 +8358,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AU15" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AV15" s="8" t="inlineStr">
+      <c r="AU15" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AV15" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -8373,14 +8373,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AX15" s="7" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AY15" s="9" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AX15" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AY15" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AZ15" s="6" t="inlineStr">
@@ -8443,12 +8443,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BL15" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BM15" s="8" t="inlineStr">
+      <c r="BL15" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BM15" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -8463,9 +8463,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BP15" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BP15" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -8490,9 +8490,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E16" s="9" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="E16" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F16" s="6" t="inlineStr">
@@ -8500,22 +8500,22 @@
           <t>API</t>
         </is>
       </c>
-      <c r="G16" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="H16" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="I16" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="J16" s="8" t="inlineStr">
+      <c r="G16" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="H16" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="I16" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="J16" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -8530,7 +8530,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="M16" s="8" t="inlineStr">
+      <c r="M16" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -8540,17 +8540,17 @@
           <t>API</t>
         </is>
       </c>
-      <c r="O16" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="P16" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Q16" s="8" t="inlineStr">
+      <c r="O16" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="P16" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Q16" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -8580,22 +8580,22 @@
           <t>API</t>
         </is>
       </c>
-      <c r="W16" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="X16" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Y16" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Z16" s="8" t="inlineStr">
+      <c r="W16" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="X16" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Y16" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Z16" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -8615,22 +8615,22 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AD16" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AE16" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AF16" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AG16" s="8" t="inlineStr">
+      <c r="AD16" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AE16" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AF16" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AG16" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -8640,7 +8640,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AI16" s="8" t="inlineStr">
+      <c r="AI16" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -8665,17 +8665,17 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AN16" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AO16" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AP16" s="8" t="inlineStr">
+      <c r="AN16" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AO16" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AP16" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -8690,7 +8690,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AS16" s="8" t="inlineStr">
+      <c r="AS16" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -8700,12 +8700,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AU16" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AV16" s="8" t="inlineStr">
+      <c r="AU16" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AV16" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -8715,14 +8715,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AX16" s="7" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AY16" s="9" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AX16" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AY16" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AZ16" s="6" t="inlineStr">
@@ -8785,12 +8785,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BL16" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BM16" s="8" t="inlineStr">
+      <c r="BL16" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BM16" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -8805,9 +8805,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BP16" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BP16" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -8832,9 +8832,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E17" s="9" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="E17" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F17" s="6" t="inlineStr">
@@ -8842,22 +8842,22 @@
           <t>API</t>
         </is>
       </c>
-      <c r="G17" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="H17" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="I17" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="J17" s="8" t="inlineStr">
+      <c r="G17" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="H17" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="I17" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="J17" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -8872,7 +8872,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="M17" s="8" t="inlineStr">
+      <c r="M17" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -8882,17 +8882,17 @@
           <t>API</t>
         </is>
       </c>
-      <c r="O17" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="P17" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Q17" s="8" t="inlineStr">
+      <c r="O17" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="P17" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Q17" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -8922,22 +8922,22 @@
           <t>API</t>
         </is>
       </c>
-      <c r="W17" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="X17" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Y17" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Z17" s="8" t="inlineStr">
+      <c r="W17" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="X17" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Y17" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Z17" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -8957,22 +8957,22 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AD17" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AE17" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AF17" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AG17" s="8" t="inlineStr">
+      <c r="AD17" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AE17" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AF17" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AG17" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -8982,7 +8982,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AI17" s="8" t="inlineStr">
+      <c r="AI17" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -9007,17 +9007,17 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AN17" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AO17" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AP17" s="8" t="inlineStr">
+      <c r="AN17" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AO17" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AP17" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -9032,7 +9032,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AS17" s="8" t="inlineStr">
+      <c r="AS17" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -9042,12 +9042,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AU17" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AV17" s="8" t="inlineStr">
+      <c r="AU17" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AV17" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -9057,14 +9057,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AX17" s="7" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AY17" s="9" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AX17" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AY17" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AZ17" s="6" t="inlineStr">
@@ -9127,12 +9127,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BL17" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BM17" s="8" t="inlineStr">
+      <c r="BL17" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BM17" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -9147,9 +9147,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BP17" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BP17" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -9174,9 +9174,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E18" s="7" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="E18" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F18" s="6" t="inlineStr">
@@ -9184,7 +9184,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="G18" s="8" t="inlineStr">
+      <c r="G18" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -9199,7 +9199,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="J18" s="8" t="inlineStr">
+      <c r="J18" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -9214,7 +9214,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="M18" s="8" t="inlineStr">
+      <c r="M18" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -9224,17 +9224,17 @@
           <t>API</t>
         </is>
       </c>
-      <c r="O18" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="P18" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Q18" s="8" t="inlineStr">
+      <c r="O18" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="P18" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Q18" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -9264,22 +9264,22 @@
           <t>API</t>
         </is>
       </c>
-      <c r="W18" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="X18" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Y18" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Z18" s="8" t="inlineStr">
+      <c r="W18" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="X18" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Y18" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Z18" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -9299,22 +9299,22 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AD18" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AE18" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AF18" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AG18" s="8" t="inlineStr">
+      <c r="AD18" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AE18" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AF18" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AG18" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -9324,7 +9324,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AI18" s="8" t="inlineStr">
+      <c r="AI18" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -9349,17 +9349,17 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AN18" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AO18" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AP18" s="8" t="inlineStr">
+      <c r="AN18" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AO18" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AP18" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -9374,7 +9374,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AS18" s="8" t="inlineStr">
+      <c r="AS18" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -9384,12 +9384,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AU18" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AV18" s="8" t="inlineStr">
+      <c r="AU18" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AV18" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -9399,14 +9399,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AX18" s="7" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AY18" s="9" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AX18" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AY18" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AZ18" s="6" t="inlineStr">
@@ -9469,12 +9469,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BL18" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BM18" s="8" t="inlineStr">
+      <c r="BL18" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BM18" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -9489,9 +9489,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BP18" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BP18" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -9516,7 +9516,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E19" s="7" t="inlineStr">
+      <c r="E19" s="8" t="inlineStr">
         <is>
           <t>AMBIGUOUS</t>
         </is>
@@ -9526,7 +9526,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="G19" s="8" t="inlineStr">
+      <c r="G19" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -9541,7 +9541,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="J19" s="8" t="inlineStr">
+      <c r="J19" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -9556,7 +9556,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="M19" s="8" t="inlineStr">
+      <c r="M19" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -9566,17 +9566,17 @@
           <t>API</t>
         </is>
       </c>
-      <c r="O19" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="P19" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Q19" s="8" t="inlineStr">
+      <c r="O19" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="P19" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Q19" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -9606,22 +9606,22 @@
           <t>API</t>
         </is>
       </c>
-      <c r="W19" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="X19" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Y19" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Z19" s="8" t="inlineStr">
+      <c r="W19" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="X19" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Y19" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Z19" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -9641,22 +9641,22 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AD19" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AE19" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AF19" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AG19" s="8" t="inlineStr">
+      <c r="AD19" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AE19" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AF19" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AG19" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -9666,7 +9666,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AI19" s="8" t="inlineStr">
+      <c r="AI19" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -9691,17 +9691,17 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AN19" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AO19" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AP19" s="8" t="inlineStr">
+      <c r="AN19" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AO19" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AP19" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -9716,7 +9716,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AS19" s="8" t="inlineStr">
+      <c r="AS19" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -9726,12 +9726,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AU19" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AV19" s="8" t="inlineStr">
+      <c r="AU19" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AV19" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -9741,7 +9741,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AX19" s="7" t="inlineStr">
+      <c r="AX19" s="8" t="inlineStr">
         <is>
           <t>AMBIGUOUS</t>
         </is>
@@ -9811,12 +9811,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BL19" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BM19" s="8" t="inlineStr">
+      <c r="BL19" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BM19" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -9858,9 +9858,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E20" s="9" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="E20" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F20" s="6" t="inlineStr">
@@ -9868,22 +9868,22 @@
           <t>API</t>
         </is>
       </c>
-      <c r="G20" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="H20" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="I20" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="J20" s="8" t="inlineStr">
+      <c r="G20" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="H20" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="I20" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="J20" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -9898,7 +9898,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="M20" s="8" t="inlineStr">
+      <c r="M20" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -9908,17 +9908,17 @@
           <t>API</t>
         </is>
       </c>
-      <c r="O20" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="P20" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Q20" s="8" t="inlineStr">
+      <c r="O20" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="P20" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Q20" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -9948,22 +9948,22 @@
           <t>API</t>
         </is>
       </c>
-      <c r="W20" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="X20" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Y20" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Z20" s="8" t="inlineStr">
+      <c r="W20" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="X20" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Y20" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Z20" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -9983,22 +9983,22 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AD20" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AE20" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AF20" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AG20" s="8" t="inlineStr">
+      <c r="AD20" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AE20" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AF20" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AG20" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -10008,7 +10008,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AI20" s="8" t="inlineStr">
+      <c r="AI20" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -10033,17 +10033,17 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AN20" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AO20" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AP20" s="8" t="inlineStr">
+      <c r="AN20" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AO20" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AP20" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -10058,7 +10058,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AS20" s="8" t="inlineStr">
+      <c r="AS20" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -10068,12 +10068,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AU20" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AV20" s="8" t="inlineStr">
+      <c r="AU20" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AV20" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -10083,14 +10083,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AX20" s="7" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AY20" s="9" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AX20" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AY20" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AZ20" s="6" t="inlineStr">
@@ -10153,12 +10153,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BL20" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BM20" s="8" t="inlineStr">
+      <c r="BL20" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BM20" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -10173,9 +10173,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BP20" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BP20" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -10200,9 +10200,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E21" s="9" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="E21" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F21" s="6" t="inlineStr">
@@ -10210,22 +10210,22 @@
           <t>API</t>
         </is>
       </c>
-      <c r="G21" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="H21" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="I21" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="J21" s="8" t="inlineStr">
+      <c r="G21" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="H21" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="I21" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="J21" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -10240,7 +10240,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="M21" s="8" t="inlineStr">
+      <c r="M21" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -10250,17 +10250,17 @@
           <t>API</t>
         </is>
       </c>
-      <c r="O21" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="P21" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Q21" s="8" t="inlineStr">
+      <c r="O21" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="P21" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Q21" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -10290,22 +10290,22 @@
           <t>API</t>
         </is>
       </c>
-      <c r="W21" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="X21" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Y21" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Z21" s="8" t="inlineStr">
+      <c r="W21" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="X21" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Y21" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Z21" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -10325,22 +10325,22 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AD21" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AE21" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AF21" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AG21" s="8" t="inlineStr">
+      <c r="AD21" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AE21" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AF21" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AG21" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -10350,7 +10350,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AI21" s="8" t="inlineStr">
+      <c r="AI21" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -10375,17 +10375,17 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AN21" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AO21" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AP21" s="8" t="inlineStr">
+      <c r="AN21" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AO21" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AP21" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -10400,7 +10400,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AS21" s="8" t="inlineStr">
+      <c r="AS21" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -10410,12 +10410,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AU21" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AV21" s="8" t="inlineStr">
+      <c r="AU21" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AV21" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -10425,14 +10425,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AX21" s="7" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AY21" s="9" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AX21" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AY21" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AZ21" s="6" t="inlineStr">
@@ -10495,12 +10495,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BL21" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BM21" s="8" t="inlineStr">
+      <c r="BL21" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BM21" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -10515,9 +10515,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BP21" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BP21" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -10542,9 +10542,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E22" s="9" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="E22" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F22" s="6" t="inlineStr">
@@ -10552,22 +10552,22 @@
           <t>API</t>
         </is>
       </c>
-      <c r="G22" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="H22" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="I22" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="J22" s="8" t="inlineStr">
+      <c r="G22" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="H22" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="I22" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="J22" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -10582,7 +10582,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="M22" s="8" t="inlineStr">
+      <c r="M22" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -10592,17 +10592,17 @@
           <t>API</t>
         </is>
       </c>
-      <c r="O22" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="P22" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Q22" s="8" t="inlineStr">
+      <c r="O22" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="P22" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Q22" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -10632,22 +10632,22 @@
           <t>API</t>
         </is>
       </c>
-      <c r="W22" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="X22" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Y22" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Z22" s="8" t="inlineStr">
+      <c r="W22" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="X22" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Y22" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Z22" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -10667,22 +10667,22 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AD22" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AE22" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AF22" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AG22" s="8" t="inlineStr">
+      <c r="AD22" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AE22" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AF22" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AG22" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -10692,7 +10692,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AI22" s="8" t="inlineStr">
+      <c r="AI22" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -10717,17 +10717,17 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AN22" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AO22" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AP22" s="8" t="inlineStr">
+      <c r="AN22" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AO22" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AP22" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -10742,7 +10742,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AS22" s="8" t="inlineStr">
+      <c r="AS22" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -10752,12 +10752,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AU22" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AV22" s="8" t="inlineStr">
+      <c r="AU22" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AV22" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -10767,14 +10767,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AX22" s="7" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AY22" s="9" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AX22" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AY22" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AZ22" s="6" t="inlineStr">
@@ -10837,12 +10837,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BL22" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BM22" s="8" t="inlineStr">
+      <c r="BL22" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BM22" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -10857,9 +10857,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BP22" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BP22" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -10884,9 +10884,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E23" s="9" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="E23" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F23" s="6" t="inlineStr">
@@ -10894,22 +10894,22 @@
           <t>API</t>
         </is>
       </c>
-      <c r="G23" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="H23" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="I23" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="J23" s="8" t="inlineStr">
+      <c r="G23" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="H23" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="I23" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="J23" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -10924,7 +10924,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="M23" s="8" t="inlineStr">
+      <c r="M23" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -10934,17 +10934,17 @@
           <t>API</t>
         </is>
       </c>
-      <c r="O23" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="P23" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Q23" s="8" t="inlineStr">
+      <c r="O23" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="P23" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Q23" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -10974,22 +10974,22 @@
           <t>API</t>
         </is>
       </c>
-      <c r="W23" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="X23" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Y23" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Z23" s="8" t="inlineStr">
+      <c r="W23" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="X23" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Y23" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Z23" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -11009,22 +11009,22 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AD23" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AE23" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AF23" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AG23" s="8" t="inlineStr">
+      <c r="AD23" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AE23" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AF23" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AG23" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -11034,7 +11034,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AI23" s="8" t="inlineStr">
+      <c r="AI23" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -11059,17 +11059,17 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AN23" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AO23" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AP23" s="8" t="inlineStr">
+      <c r="AN23" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AO23" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AP23" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -11084,7 +11084,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AS23" s="8" t="inlineStr">
+      <c r="AS23" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -11094,12 +11094,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AU23" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AV23" s="8" t="inlineStr">
+      <c r="AU23" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AV23" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -11109,14 +11109,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AX23" s="7" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AY23" s="9" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AX23" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AY23" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AZ23" s="6" t="inlineStr">
@@ -11179,12 +11179,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BL23" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BM23" s="8" t="inlineStr">
+      <c r="BL23" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BM23" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -11199,9 +11199,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BP23" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BP23" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -11226,9 +11226,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E24" s="9" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="E24" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F24" s="6" t="inlineStr">
@@ -11236,22 +11236,22 @@
           <t>API</t>
         </is>
       </c>
-      <c r="G24" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="H24" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="I24" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="J24" s="8" t="inlineStr">
+      <c r="G24" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="H24" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="I24" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="J24" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -11266,7 +11266,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="M24" s="8" t="inlineStr">
+      <c r="M24" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -11276,17 +11276,17 @@
           <t>API</t>
         </is>
       </c>
-      <c r="O24" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="P24" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Q24" s="8" t="inlineStr">
+      <c r="O24" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="P24" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Q24" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -11316,22 +11316,22 @@
           <t>API</t>
         </is>
       </c>
-      <c r="W24" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="X24" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Y24" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Z24" s="8" t="inlineStr">
+      <c r="W24" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="X24" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Y24" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Z24" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -11351,22 +11351,22 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AD24" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AE24" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AF24" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AG24" s="8" t="inlineStr">
+      <c r="AD24" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AE24" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AF24" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AG24" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -11376,7 +11376,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AI24" s="8" t="inlineStr">
+      <c r="AI24" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -11401,17 +11401,17 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AN24" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AO24" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AP24" s="8" t="inlineStr">
+      <c r="AN24" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AO24" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AP24" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -11426,7 +11426,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AS24" s="8" t="inlineStr">
+      <c r="AS24" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -11436,12 +11436,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AU24" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AV24" s="8" t="inlineStr">
+      <c r="AU24" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AV24" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -11451,14 +11451,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AX24" s="7" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AY24" s="9" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AX24" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AY24" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AZ24" s="6" t="inlineStr">
@@ -11521,12 +11521,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BL24" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BM24" s="8" t="inlineStr">
+      <c r="BL24" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BM24" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -11541,9 +11541,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BP24" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BP24" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -11568,9 +11568,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E25" s="9" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="E25" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F25" s="6" t="inlineStr">
@@ -11578,22 +11578,22 @@
           <t>API</t>
         </is>
       </c>
-      <c r="G25" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="H25" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="I25" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="J25" s="8" t="inlineStr">
+      <c r="G25" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="H25" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="I25" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="J25" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -11608,7 +11608,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="M25" s="8" t="inlineStr">
+      <c r="M25" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -11618,17 +11618,17 @@
           <t>API</t>
         </is>
       </c>
-      <c r="O25" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="P25" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Q25" s="8" t="inlineStr">
+      <c r="O25" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="P25" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Q25" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -11658,22 +11658,22 @@
           <t>API</t>
         </is>
       </c>
-      <c r="W25" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="X25" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Y25" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Z25" s="8" t="inlineStr">
+      <c r="W25" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="X25" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Y25" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Z25" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -11693,22 +11693,22 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AD25" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AE25" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AF25" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AG25" s="8" t="inlineStr">
+      <c r="AD25" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AE25" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AF25" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AG25" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -11718,7 +11718,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AI25" s="8" t="inlineStr">
+      <c r="AI25" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -11743,17 +11743,17 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AN25" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AO25" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AP25" s="8" t="inlineStr">
+      <c r="AN25" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AO25" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AP25" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -11768,7 +11768,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AS25" s="8" t="inlineStr">
+      <c r="AS25" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -11778,12 +11778,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AU25" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AV25" s="8" t="inlineStr">
+      <c r="AU25" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AV25" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -11793,14 +11793,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AX25" s="7" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AY25" s="9" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AX25" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AY25" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AZ25" s="6" t="inlineStr">
@@ -11863,12 +11863,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BL25" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BM25" s="8" t="inlineStr">
+      <c r="BL25" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BM25" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -11883,9 +11883,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BP25" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BP25" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -11910,9 +11910,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E26" s="9" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="E26" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F26" s="6" t="inlineStr">
@@ -11920,22 +11920,22 @@
           <t>API</t>
         </is>
       </c>
-      <c r="G26" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="H26" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="I26" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="J26" s="8" t="inlineStr">
+      <c r="G26" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="H26" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="I26" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="J26" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -11950,7 +11950,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="M26" s="8" t="inlineStr">
+      <c r="M26" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -11960,17 +11960,17 @@
           <t>API</t>
         </is>
       </c>
-      <c r="O26" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="P26" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Q26" s="8" t="inlineStr">
+      <c r="O26" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="P26" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Q26" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -12000,22 +12000,22 @@
           <t>API</t>
         </is>
       </c>
-      <c r="W26" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="X26" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Y26" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Z26" s="8" t="inlineStr">
+      <c r="W26" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="X26" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Y26" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Z26" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -12035,22 +12035,22 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AD26" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AE26" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AF26" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AG26" s="8" t="inlineStr">
+      <c r="AD26" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AE26" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AF26" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AG26" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -12060,7 +12060,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AI26" s="8" t="inlineStr">
+      <c r="AI26" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -12085,17 +12085,17 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AN26" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AO26" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AP26" s="8" t="inlineStr">
+      <c r="AN26" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AO26" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AP26" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -12110,7 +12110,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AS26" s="8" t="inlineStr">
+      <c r="AS26" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -12120,12 +12120,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AU26" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AV26" s="8" t="inlineStr">
+      <c r="AU26" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AV26" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -12135,14 +12135,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AX26" s="7" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AY26" s="9" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AX26" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AY26" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AZ26" s="6" t="inlineStr">
@@ -12205,12 +12205,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BL26" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BM26" s="8" t="inlineStr">
+      <c r="BL26" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BM26" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -12225,9 +12225,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BP26" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BP26" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -12262,22 +12262,22 @@
           <t>API</t>
         </is>
       </c>
-      <c r="G27" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="H27" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="I27" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="J27" s="8" t="inlineStr">
+      <c r="G27" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="H27" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="I27" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="J27" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -12292,7 +12292,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="M27" s="8" t="inlineStr">
+      <c r="M27" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -12302,17 +12302,17 @@
           <t>API</t>
         </is>
       </c>
-      <c r="O27" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="P27" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Q27" s="8" t="inlineStr">
+      <c r="O27" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="P27" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Q27" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -12342,22 +12342,22 @@
           <t>API</t>
         </is>
       </c>
-      <c r="W27" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="X27" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Y27" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Z27" s="8" t="inlineStr">
+      <c r="W27" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="X27" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Y27" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Z27" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -12377,22 +12377,22 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AD27" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AE27" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AF27" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AG27" s="8" t="inlineStr">
+      <c r="AD27" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AE27" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AF27" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AG27" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -12402,7 +12402,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AI27" s="8" t="inlineStr">
+      <c r="AI27" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -12427,17 +12427,17 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AN27" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AO27" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AP27" s="8" t="inlineStr">
+      <c r="AN27" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AO27" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AP27" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -12452,7 +12452,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AS27" s="8" t="inlineStr">
+      <c r="AS27" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -12462,12 +12462,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AU27" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AV27" s="8" t="inlineStr">
+      <c r="AU27" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AV27" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -12477,7 +12477,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AX27" s="7" t="inlineStr">
+      <c r="AX27" s="8" t="inlineStr">
         <is>
           <t>AMBIGUOUS</t>
         </is>
@@ -12547,12 +12547,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BL27" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BM27" s="8" t="inlineStr">
+      <c r="BL27" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BM27" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -12588,7 +12588,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D21"/>
+  <dimension ref="A1:D4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -12622,7 +12622,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>STM32WL54CC</t>
+          <t>STM32WL55CC</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -12644,7 +12644,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>STM32WL54CC</t>
+          <t>STM32WL55CC</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -12659,14 +12659,14 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Table 26. General operating conditions: V_DD min reads '1.8(1)' — the footnote qualifies the figure</t>
+          <t>Table 26. General operating conditions: V_DD min reads '1.8(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>STM32WLE4C8</t>
+          <t>STM32WLE5C8</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -12681,381 +12681,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Table 26. General operating conditions: V_DD min reads '1.8(1)' — the footnote qualifies the figure</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>STM32WLE5JB</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Supply Voltage (V) min</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>Table 26. General operating conditions: V_DD min reads '1.8(1)' — the footnote qualifies the figure</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>STM32WL54JC</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Core</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>cover names Arm Cortex-M4, Arm Cortex-M0+; ST reports the application core here and the others as co-processors</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>STM32WL54JC</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>Supply Voltage (V) min</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>Table 26. General operating conditions: V_DD min reads '1.8(1)' — the footnote qualifies the figure</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>STM32WLE5CC</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>Supply Voltage (V) min</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>Table 26. General operating conditions: V_DD min reads '1.8(1)' — the footnote qualifies the figure</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>STM32WLE5JC</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>Supply Voltage (V) min</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>Table 26. General operating conditions: V_DD min reads '1.8(1)' — the footnote qualifies the figure</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>STM32WL55JC</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>Core</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>cover names Arm Cortex-M4, Arm Cortex-M0+; ST reports the application core here and the others as co-processors</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>STM32WL55JC</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>Supply Voltage (V) min</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>Table 26. General operating conditions: V_DD min reads '1.8(1)' — the footnote qualifies the figure</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>STM32WL55CC</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>Core</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>cover names Arm Cortex-M4, Arm Cortex-M0+; ST reports the application core here and the others as co-processors</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>STM32WL55CC</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>Supply Voltage (V) min</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>Table 26. General operating conditions: V_DD min reads '1.8(1)' — the footnote qualifies the figure</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>STM32WLE5J8</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>Supply Voltage (V) min</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>Table 26. General operating conditions: V_DD min reads '1.8(1)' — the footnote qualifies the figure</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>STM32WLE4J8</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>Supply Voltage (V) min</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>Table 26. General operating conditions: V_DD min reads '1.8(1)' — the footnote qualifies the figure</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>STM32WLE4JB</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>Supply Voltage (V) min</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>Table 26. General operating conditions: V_DD min reads '1.8(1)' — the footnote qualifies the figure</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>STM32WLE4CB</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>Supply Voltage (V) min</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>Table 26. General operating conditions: V_DD min reads '1.8(1)' — the footnote qualifies the figure</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>STM32WLE4CC</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>Supply Voltage (V) min</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>Table 26. General operating conditions: V_DD min reads '1.8(1)' — the footnote qualifies the figure</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>STM32WLE4JC</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>Supply Voltage (V) min</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>Table 26. General operating conditions: V_DD min reads '1.8(1)' — the footnote qualifies the figure</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>STM32WLE5CB</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>Supply Voltage (V) min</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>Table 26. General operating conditions: V_DD min reads '1.8(1)' — the footnote qualifies the figure</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>STM32WLE5C8</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>Supply Voltage (V) min</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>Table 26. General operating conditions: V_DD min reads '1.8(1)' — the footnote qualifies the figure</t>
+          <t>Table 26. General operating conditions: V_DD min reads '1.8(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>

--- a/product_selector_out/STM32WL5x-Ex.xlsx
+++ b/product_selector_out/STM32WL5x-Ex.xlsx
@@ -61,12 +61,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00F2F2F2"/>
+        <fgColor rgb="00FFEB9C"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFEB9C"/>
+        <fgColor rgb="00F2F2F2"/>
       </patternFill>
     </fill>
     <fill>
@@ -1350,7 +1350,7 @@
       </c>
       <c r="BP12" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://www.st.com/resource/en/datasheet/stm32wl55cc.pdf</t>
         </is>
       </c>
     </row>
@@ -1692,7 +1692,7 @@
       </c>
       <c r="BP13" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://www.st.com/resource/en/datasheet/stm32wle5c8.pdf</t>
         </is>
       </c>
     </row>
@@ -2034,7 +2034,7 @@
       </c>
       <c r="BP14" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://www.st.com/resource/en/datasheet/stm32wle5c8.pdf</t>
         </is>
       </c>
     </row>
@@ -2376,7 +2376,7 @@
       </c>
       <c r="BP15" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://www.st.com/resource/en/datasheet/stm32wl55cc.pdf</t>
         </is>
       </c>
     </row>
@@ -2718,7 +2718,7 @@
       </c>
       <c r="BP16" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://www.st.com/resource/en/datasheet/stm32wle5c8.pdf</t>
         </is>
       </c>
     </row>
@@ -3060,7 +3060,7 @@
       </c>
       <c r="BP17" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://www.st.com/resource/en/datasheet/stm32wle5c8.pdf</t>
         </is>
       </c>
     </row>
@@ -3402,7 +3402,7 @@
       </c>
       <c r="BP18" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://www.st.com/resource/en/datasheet/stm32wl55cc.pdf</t>
         </is>
       </c>
     </row>
@@ -4086,7 +4086,7 @@
       </c>
       <c r="BP20" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://www.st.com/resource/en/datasheet/stm32wle5c8.pdf</t>
         </is>
       </c>
     </row>
@@ -4428,7 +4428,7 @@
       </c>
       <c r="BP21" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://www.st.com/resource/en/datasheet/stm32wle5c8.pdf</t>
         </is>
       </c>
     </row>
@@ -4770,7 +4770,7 @@
       </c>
       <c r="BP22" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://www.st.com/resource/en/datasheet/stm32wle5c8.pdf</t>
         </is>
       </c>
     </row>
@@ -5112,7 +5112,7 @@
       </c>
       <c r="BP23" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://www.st.com/resource/en/datasheet/stm32wle5c8.pdf</t>
         </is>
       </c>
     </row>
@@ -5454,7 +5454,7 @@
       </c>
       <c r="BP24" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://www.st.com/resource/en/datasheet/stm32wle5c8.pdf</t>
         </is>
       </c>
     </row>
@@ -5796,7 +5796,7 @@
       </c>
       <c r="BP25" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://www.st.com/resource/en/datasheet/stm32wle5c8.pdf</t>
         </is>
       </c>
     </row>
@@ -6138,7 +6138,7 @@
       </c>
       <c r="BP26" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://www.st.com/resource/en/datasheet/stm32wle5c8.pdf</t>
         </is>
       </c>
     </row>
@@ -7122,9 +7122,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E12" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="E12" s="7" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="F12" s="6" t="inlineStr">
@@ -7132,7 +7132,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="G12" s="7" t="inlineStr">
+      <c r="G12" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -7147,7 +7147,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="J12" s="7" t="inlineStr">
+      <c r="J12" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -7162,7 +7162,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="M12" s="7" t="inlineStr">
+      <c r="M12" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -7172,17 +7172,17 @@
           <t>API</t>
         </is>
       </c>
-      <c r="O12" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="P12" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Q12" s="7" t="inlineStr">
+      <c r="O12" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="P12" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Q12" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -7212,22 +7212,22 @@
           <t>API</t>
         </is>
       </c>
-      <c r="W12" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="X12" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Y12" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Z12" s="7" t="inlineStr">
+      <c r="W12" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="X12" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Y12" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Z12" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -7247,22 +7247,22 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AD12" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AE12" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AF12" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AG12" s="7" t="inlineStr">
+      <c r="AD12" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AE12" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AF12" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AG12" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -7272,7 +7272,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AI12" s="7" t="inlineStr">
+      <c r="AI12" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -7297,17 +7297,17 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AN12" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AO12" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AP12" s="7" t="inlineStr">
+      <c r="AN12" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AO12" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AP12" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -7322,7 +7322,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AS12" s="7" t="inlineStr">
+      <c r="AS12" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -7332,12 +7332,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AU12" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AV12" s="7" t="inlineStr">
+      <c r="AU12" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AV12" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -7347,14 +7347,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AX12" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="AY12" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AX12" s="7" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="AY12" s="9" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AZ12" s="6" t="inlineStr">
@@ -7417,12 +7417,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BL12" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BM12" s="7" t="inlineStr">
+      <c r="BL12" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BM12" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -7437,9 +7437,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BP12" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
+      <c r="BP12" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
     </row>
@@ -7464,9 +7464,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E13" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="E13" s="9" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="F13" s="6" t="inlineStr">
@@ -7474,22 +7474,22 @@
           <t>API</t>
         </is>
       </c>
-      <c r="G13" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="H13" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="I13" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="J13" s="7" t="inlineStr">
+      <c r="G13" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="H13" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="I13" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="J13" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -7504,7 +7504,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="M13" s="7" t="inlineStr">
+      <c r="M13" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -7514,17 +7514,17 @@
           <t>API</t>
         </is>
       </c>
-      <c r="O13" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="P13" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Q13" s="7" t="inlineStr">
+      <c r="O13" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="P13" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Q13" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -7554,22 +7554,22 @@
           <t>API</t>
         </is>
       </c>
-      <c r="W13" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="X13" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Y13" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Z13" s="7" t="inlineStr">
+      <c r="W13" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="X13" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Y13" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Z13" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -7589,22 +7589,22 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AD13" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AE13" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AF13" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AG13" s="7" t="inlineStr">
+      <c r="AD13" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AE13" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AF13" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AG13" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -7614,7 +7614,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AI13" s="7" t="inlineStr">
+      <c r="AI13" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -7639,17 +7639,17 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AN13" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AO13" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AP13" s="7" t="inlineStr">
+      <c r="AN13" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AO13" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AP13" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -7664,7 +7664,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AS13" s="7" t="inlineStr">
+      <c r="AS13" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -7674,12 +7674,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AU13" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AV13" s="7" t="inlineStr">
+      <c r="AU13" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AV13" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -7689,14 +7689,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AX13" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="AY13" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AX13" s="7" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="AY13" s="9" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AZ13" s="6" t="inlineStr">
@@ -7759,12 +7759,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BL13" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BM13" s="7" t="inlineStr">
+      <c r="BL13" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BM13" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -7779,9 +7779,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BP13" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
+      <c r="BP13" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
     </row>
@@ -7806,9 +7806,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E14" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="E14" s="9" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="F14" s="6" t="inlineStr">
@@ -7816,22 +7816,22 @@
           <t>API</t>
         </is>
       </c>
-      <c r="G14" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="H14" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="I14" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="J14" s="7" t="inlineStr">
+      <c r="G14" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="H14" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="I14" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="J14" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -7846,7 +7846,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="M14" s="7" t="inlineStr">
+      <c r="M14" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -7856,17 +7856,17 @@
           <t>API</t>
         </is>
       </c>
-      <c r="O14" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="P14" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Q14" s="7" t="inlineStr">
+      <c r="O14" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="P14" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Q14" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -7896,22 +7896,22 @@
           <t>API</t>
         </is>
       </c>
-      <c r="W14" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="X14" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Y14" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Z14" s="7" t="inlineStr">
+      <c r="W14" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="X14" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Y14" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Z14" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -7931,22 +7931,22 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AD14" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AE14" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AF14" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AG14" s="7" t="inlineStr">
+      <c r="AD14" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AE14" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AF14" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AG14" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -7956,7 +7956,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AI14" s="7" t="inlineStr">
+      <c r="AI14" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -7981,17 +7981,17 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AN14" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AO14" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AP14" s="7" t="inlineStr">
+      <c r="AN14" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AO14" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AP14" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -8006,7 +8006,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AS14" s="7" t="inlineStr">
+      <c r="AS14" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -8016,12 +8016,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AU14" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AV14" s="7" t="inlineStr">
+      <c r="AU14" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AV14" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -8031,14 +8031,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AX14" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="AY14" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AX14" s="7" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="AY14" s="9" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AZ14" s="6" t="inlineStr">
@@ -8101,12 +8101,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BL14" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BM14" s="7" t="inlineStr">
+      <c r="BL14" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BM14" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -8121,9 +8121,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BP14" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
+      <c r="BP14" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
     </row>
@@ -8148,9 +8148,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E15" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="E15" s="7" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="F15" s="6" t="inlineStr">
@@ -8158,7 +8158,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="G15" s="7" t="inlineStr">
+      <c r="G15" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -8173,7 +8173,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="J15" s="7" t="inlineStr">
+      <c r="J15" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -8188,7 +8188,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="M15" s="7" t="inlineStr">
+      <c r="M15" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -8198,17 +8198,17 @@
           <t>API</t>
         </is>
       </c>
-      <c r="O15" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="P15" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Q15" s="7" t="inlineStr">
+      <c r="O15" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="P15" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Q15" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -8238,22 +8238,22 @@
           <t>API</t>
         </is>
       </c>
-      <c r="W15" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="X15" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Y15" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Z15" s="7" t="inlineStr">
+      <c r="W15" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="X15" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Y15" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Z15" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -8273,22 +8273,22 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AD15" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AE15" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AF15" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AG15" s="7" t="inlineStr">
+      <c r="AD15" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AE15" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AF15" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AG15" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -8298,7 +8298,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AI15" s="7" t="inlineStr">
+      <c r="AI15" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -8323,17 +8323,17 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AN15" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AO15" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AP15" s="7" t="inlineStr">
+      <c r="AN15" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AO15" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AP15" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -8348,7 +8348,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AS15" s="7" t="inlineStr">
+      <c r="AS15" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -8358,12 +8358,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AU15" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AV15" s="7" t="inlineStr">
+      <c r="AU15" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AV15" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -8373,14 +8373,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AX15" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="AY15" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AX15" s="7" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="AY15" s="9" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AZ15" s="6" t="inlineStr">
@@ -8443,12 +8443,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BL15" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BM15" s="7" t="inlineStr">
+      <c r="BL15" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BM15" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -8463,9 +8463,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BP15" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
+      <c r="BP15" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
     </row>
@@ -8490,9 +8490,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E16" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="E16" s="9" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="F16" s="6" t="inlineStr">
@@ -8500,22 +8500,22 @@
           <t>API</t>
         </is>
       </c>
-      <c r="G16" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="H16" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="I16" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="J16" s="7" t="inlineStr">
+      <c r="G16" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="H16" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="I16" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="J16" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -8530,7 +8530,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="M16" s="7" t="inlineStr">
+      <c r="M16" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -8540,17 +8540,17 @@
           <t>API</t>
         </is>
       </c>
-      <c r="O16" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="P16" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Q16" s="7" t="inlineStr">
+      <c r="O16" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="P16" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Q16" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -8580,22 +8580,22 @@
           <t>API</t>
         </is>
       </c>
-      <c r="W16" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="X16" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Y16" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Z16" s="7" t="inlineStr">
+      <c r="W16" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="X16" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Y16" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Z16" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -8615,22 +8615,22 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AD16" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AE16" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AF16" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AG16" s="7" t="inlineStr">
+      <c r="AD16" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AE16" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AF16" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AG16" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -8640,7 +8640,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AI16" s="7" t="inlineStr">
+      <c r="AI16" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -8665,17 +8665,17 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AN16" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AO16" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AP16" s="7" t="inlineStr">
+      <c r="AN16" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AO16" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AP16" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -8690,7 +8690,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AS16" s="7" t="inlineStr">
+      <c r="AS16" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -8700,12 +8700,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AU16" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AV16" s="7" t="inlineStr">
+      <c r="AU16" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AV16" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -8715,14 +8715,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AX16" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="AY16" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AX16" s="7" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="AY16" s="9" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AZ16" s="6" t="inlineStr">
@@ -8785,12 +8785,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BL16" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BM16" s="7" t="inlineStr">
+      <c r="BL16" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BM16" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -8805,9 +8805,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BP16" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
+      <c r="BP16" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
     </row>
@@ -8832,9 +8832,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E17" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="E17" s="9" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="F17" s="6" t="inlineStr">
@@ -8842,22 +8842,22 @@
           <t>API</t>
         </is>
       </c>
-      <c r="G17" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="H17" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="I17" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="J17" s="7" t="inlineStr">
+      <c r="G17" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="H17" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="I17" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="J17" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -8872,7 +8872,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="M17" s="7" t="inlineStr">
+      <c r="M17" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -8882,17 +8882,17 @@
           <t>API</t>
         </is>
       </c>
-      <c r="O17" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="P17" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Q17" s="7" t="inlineStr">
+      <c r="O17" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="P17" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Q17" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -8922,22 +8922,22 @@
           <t>API</t>
         </is>
       </c>
-      <c r="W17" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="X17" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Y17" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Z17" s="7" t="inlineStr">
+      <c r="W17" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="X17" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Y17" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Z17" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -8957,22 +8957,22 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AD17" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AE17" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AF17" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AG17" s="7" t="inlineStr">
+      <c r="AD17" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AE17" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AF17" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AG17" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -8982,7 +8982,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AI17" s="7" t="inlineStr">
+      <c r="AI17" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -9007,17 +9007,17 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AN17" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AO17" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AP17" s="7" t="inlineStr">
+      <c r="AN17" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AO17" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AP17" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -9032,7 +9032,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AS17" s="7" t="inlineStr">
+      <c r="AS17" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -9042,12 +9042,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AU17" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AV17" s="7" t="inlineStr">
+      <c r="AU17" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AV17" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -9057,14 +9057,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AX17" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="AY17" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AX17" s="7" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="AY17" s="9" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AZ17" s="6" t="inlineStr">
@@ -9127,12 +9127,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BL17" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BM17" s="7" t="inlineStr">
+      <c r="BL17" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BM17" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -9147,9 +9147,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BP17" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
+      <c r="BP17" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
     </row>
@@ -9174,9 +9174,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E18" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="E18" s="7" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="F18" s="6" t="inlineStr">
@@ -9184,7 +9184,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="G18" s="7" t="inlineStr">
+      <c r="G18" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -9199,7 +9199,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="J18" s="7" t="inlineStr">
+      <c r="J18" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -9214,7 +9214,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="M18" s="7" t="inlineStr">
+      <c r="M18" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -9224,17 +9224,17 @@
           <t>API</t>
         </is>
       </c>
-      <c r="O18" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="P18" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Q18" s="7" t="inlineStr">
+      <c r="O18" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="P18" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Q18" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -9264,22 +9264,22 @@
           <t>API</t>
         </is>
       </c>
-      <c r="W18" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="X18" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Y18" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Z18" s="7" t="inlineStr">
+      <c r="W18" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="X18" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Y18" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Z18" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -9299,22 +9299,22 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AD18" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AE18" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AF18" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AG18" s="7" t="inlineStr">
+      <c r="AD18" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AE18" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AF18" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AG18" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -9324,7 +9324,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AI18" s="7" t="inlineStr">
+      <c r="AI18" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -9349,17 +9349,17 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AN18" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AO18" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AP18" s="7" t="inlineStr">
+      <c r="AN18" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AO18" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AP18" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -9374,7 +9374,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AS18" s="7" t="inlineStr">
+      <c r="AS18" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -9384,12 +9384,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AU18" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AV18" s="7" t="inlineStr">
+      <c r="AU18" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AV18" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -9399,14 +9399,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AX18" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="AY18" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AX18" s="7" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="AY18" s="9" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AZ18" s="6" t="inlineStr">
@@ -9469,12 +9469,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BL18" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BM18" s="7" t="inlineStr">
+      <c r="BL18" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BM18" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -9489,9 +9489,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BP18" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
+      <c r="BP18" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
     </row>
@@ -9516,7 +9516,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E19" s="8" t="inlineStr">
+      <c r="E19" s="7" t="inlineStr">
         <is>
           <t>AMBIGUOUS</t>
         </is>
@@ -9526,7 +9526,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="G19" s="7" t="inlineStr">
+      <c r="G19" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -9541,7 +9541,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="J19" s="7" t="inlineStr">
+      <c r="J19" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -9556,7 +9556,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="M19" s="7" t="inlineStr">
+      <c r="M19" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -9566,17 +9566,17 @@
           <t>API</t>
         </is>
       </c>
-      <c r="O19" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="P19" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Q19" s="7" t="inlineStr">
+      <c r="O19" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="P19" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Q19" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -9606,22 +9606,22 @@
           <t>API</t>
         </is>
       </c>
-      <c r="W19" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="X19" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Y19" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Z19" s="7" t="inlineStr">
+      <c r="W19" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="X19" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Y19" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Z19" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -9641,22 +9641,22 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AD19" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AE19" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AF19" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AG19" s="7" t="inlineStr">
+      <c r="AD19" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AE19" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AF19" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AG19" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -9666,7 +9666,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AI19" s="7" t="inlineStr">
+      <c r="AI19" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -9691,17 +9691,17 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AN19" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AO19" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AP19" s="7" t="inlineStr">
+      <c r="AN19" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AO19" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AP19" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -9716,7 +9716,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AS19" s="7" t="inlineStr">
+      <c r="AS19" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -9726,12 +9726,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AU19" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AV19" s="7" t="inlineStr">
+      <c r="AU19" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AV19" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -9741,7 +9741,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AX19" s="8" t="inlineStr">
+      <c r="AX19" s="7" t="inlineStr">
         <is>
           <t>AMBIGUOUS</t>
         </is>
@@ -9811,12 +9811,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BL19" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BM19" s="7" t="inlineStr">
+      <c r="BL19" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BM19" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -9858,9 +9858,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E20" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="E20" s="9" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="F20" s="6" t="inlineStr">
@@ -9868,22 +9868,22 @@
           <t>API</t>
         </is>
       </c>
-      <c r="G20" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="H20" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="I20" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="J20" s="7" t="inlineStr">
+      <c r="G20" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="H20" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="I20" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="J20" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -9898,7 +9898,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="M20" s="7" t="inlineStr">
+      <c r="M20" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -9908,17 +9908,17 @@
           <t>API</t>
         </is>
       </c>
-      <c r="O20" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="P20" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Q20" s="7" t="inlineStr">
+      <c r="O20" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="P20" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Q20" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -9948,22 +9948,22 @@
           <t>API</t>
         </is>
       </c>
-      <c r="W20" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="X20" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Y20" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Z20" s="7" t="inlineStr">
+      <c r="W20" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="X20" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Y20" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Z20" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -9983,22 +9983,22 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AD20" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AE20" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AF20" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AG20" s="7" t="inlineStr">
+      <c r="AD20" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AE20" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AF20" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AG20" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -10008,7 +10008,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AI20" s="7" t="inlineStr">
+      <c r="AI20" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -10033,17 +10033,17 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AN20" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AO20" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AP20" s="7" t="inlineStr">
+      <c r="AN20" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AO20" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AP20" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -10058,7 +10058,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AS20" s="7" t="inlineStr">
+      <c r="AS20" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -10068,12 +10068,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AU20" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AV20" s="7" t="inlineStr">
+      <c r="AU20" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AV20" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -10083,14 +10083,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AX20" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="AY20" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AX20" s="7" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="AY20" s="9" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AZ20" s="6" t="inlineStr">
@@ -10153,12 +10153,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BL20" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BM20" s="7" t="inlineStr">
+      <c r="BL20" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BM20" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -10173,9 +10173,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BP20" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
+      <c r="BP20" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
     </row>
@@ -10200,9 +10200,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E21" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="E21" s="9" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="F21" s="6" t="inlineStr">
@@ -10210,22 +10210,22 @@
           <t>API</t>
         </is>
       </c>
-      <c r="G21" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="H21" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="I21" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="J21" s="7" t="inlineStr">
+      <c r="G21" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="H21" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="I21" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="J21" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -10240,7 +10240,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="M21" s="7" t="inlineStr">
+      <c r="M21" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -10250,17 +10250,17 @@
           <t>API</t>
         </is>
       </c>
-      <c r="O21" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="P21" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Q21" s="7" t="inlineStr">
+      <c r="O21" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="P21" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Q21" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -10290,22 +10290,22 @@
           <t>API</t>
         </is>
       </c>
-      <c r="W21" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="X21" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Y21" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Z21" s="7" t="inlineStr">
+      <c r="W21" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="X21" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Y21" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Z21" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -10325,22 +10325,22 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AD21" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AE21" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AF21" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AG21" s="7" t="inlineStr">
+      <c r="AD21" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AE21" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AF21" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AG21" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -10350,7 +10350,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AI21" s="7" t="inlineStr">
+      <c r="AI21" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -10375,17 +10375,17 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AN21" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AO21" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AP21" s="7" t="inlineStr">
+      <c r="AN21" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AO21" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AP21" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -10400,7 +10400,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AS21" s="7" t="inlineStr">
+      <c r="AS21" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -10410,12 +10410,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AU21" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AV21" s="7" t="inlineStr">
+      <c r="AU21" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AV21" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -10425,14 +10425,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AX21" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="AY21" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AX21" s="7" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="AY21" s="9" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AZ21" s="6" t="inlineStr">
@@ -10495,12 +10495,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BL21" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BM21" s="7" t="inlineStr">
+      <c r="BL21" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BM21" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -10515,9 +10515,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BP21" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
+      <c r="BP21" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
     </row>
@@ -10542,9 +10542,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E22" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="E22" s="9" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="F22" s="6" t="inlineStr">
@@ -10552,22 +10552,22 @@
           <t>API</t>
         </is>
       </c>
-      <c r="G22" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="H22" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="I22" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="J22" s="7" t="inlineStr">
+      <c r="G22" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="H22" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="I22" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="J22" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -10582,7 +10582,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="M22" s="7" t="inlineStr">
+      <c r="M22" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -10592,17 +10592,17 @@
           <t>API</t>
         </is>
       </c>
-      <c r="O22" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="P22" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Q22" s="7" t="inlineStr">
+      <c r="O22" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="P22" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Q22" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -10632,22 +10632,22 @@
           <t>API</t>
         </is>
       </c>
-      <c r="W22" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="X22" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Y22" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Z22" s="7" t="inlineStr">
+      <c r="W22" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="X22" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Y22" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Z22" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -10667,22 +10667,22 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AD22" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AE22" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AF22" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AG22" s="7" t="inlineStr">
+      <c r="AD22" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AE22" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AF22" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AG22" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -10692,7 +10692,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AI22" s="7" t="inlineStr">
+      <c r="AI22" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -10717,17 +10717,17 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AN22" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AO22" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AP22" s="7" t="inlineStr">
+      <c r="AN22" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AO22" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AP22" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -10742,7 +10742,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AS22" s="7" t="inlineStr">
+      <c r="AS22" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -10752,12 +10752,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AU22" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AV22" s="7" t="inlineStr">
+      <c r="AU22" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AV22" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -10767,14 +10767,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AX22" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="AY22" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AX22" s="7" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="AY22" s="9" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AZ22" s="6" t="inlineStr">
@@ -10837,12 +10837,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BL22" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BM22" s="7" t="inlineStr">
+      <c r="BL22" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BM22" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -10857,9 +10857,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BP22" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
+      <c r="BP22" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
     </row>
@@ -10884,9 +10884,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E23" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="E23" s="9" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="F23" s="6" t="inlineStr">
@@ -10894,22 +10894,22 @@
           <t>API</t>
         </is>
       </c>
-      <c r="G23" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="H23" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="I23" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="J23" s="7" t="inlineStr">
+      <c r="G23" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="H23" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="I23" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="J23" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -10924,7 +10924,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="M23" s="7" t="inlineStr">
+      <c r="M23" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -10934,17 +10934,17 @@
           <t>API</t>
         </is>
       </c>
-      <c r="O23" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="P23" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Q23" s="7" t="inlineStr">
+      <c r="O23" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="P23" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Q23" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -10974,22 +10974,22 @@
           <t>API</t>
         </is>
       </c>
-      <c r="W23" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="X23" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Y23" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Z23" s="7" t="inlineStr">
+      <c r="W23" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="X23" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Y23" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Z23" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -11009,22 +11009,22 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AD23" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AE23" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AF23" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AG23" s="7" t="inlineStr">
+      <c r="AD23" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AE23" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AF23" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AG23" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -11034,7 +11034,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AI23" s="7" t="inlineStr">
+      <c r="AI23" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -11059,17 +11059,17 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AN23" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AO23" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AP23" s="7" t="inlineStr">
+      <c r="AN23" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AO23" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AP23" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -11084,7 +11084,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AS23" s="7" t="inlineStr">
+      <c r="AS23" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -11094,12 +11094,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AU23" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AV23" s="7" t="inlineStr">
+      <c r="AU23" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AV23" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -11109,14 +11109,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AX23" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="AY23" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AX23" s="7" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="AY23" s="9" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AZ23" s="6" t="inlineStr">
@@ -11179,12 +11179,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BL23" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BM23" s="7" t="inlineStr">
+      <c r="BL23" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BM23" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -11199,9 +11199,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BP23" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
+      <c r="BP23" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
     </row>
@@ -11226,9 +11226,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E24" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="E24" s="9" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="F24" s="6" t="inlineStr">
@@ -11236,22 +11236,22 @@
           <t>API</t>
         </is>
       </c>
-      <c r="G24" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="H24" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="I24" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="J24" s="7" t="inlineStr">
+      <c r="G24" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="H24" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="I24" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="J24" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -11266,7 +11266,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="M24" s="7" t="inlineStr">
+      <c r="M24" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -11276,17 +11276,17 @@
           <t>API</t>
         </is>
       </c>
-      <c r="O24" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="P24" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Q24" s="7" t="inlineStr">
+      <c r="O24" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="P24" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Q24" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -11316,22 +11316,22 @@
           <t>API</t>
         </is>
       </c>
-      <c r="W24" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="X24" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Y24" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Z24" s="7" t="inlineStr">
+      <c r="W24" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="X24" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Y24" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Z24" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -11351,22 +11351,22 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AD24" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AE24" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AF24" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AG24" s="7" t="inlineStr">
+      <c r="AD24" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AE24" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AF24" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AG24" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -11376,7 +11376,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AI24" s="7" t="inlineStr">
+      <c r="AI24" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -11401,17 +11401,17 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AN24" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AO24" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AP24" s="7" t="inlineStr">
+      <c r="AN24" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AO24" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AP24" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -11426,7 +11426,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AS24" s="7" t="inlineStr">
+      <c r="AS24" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -11436,12 +11436,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AU24" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AV24" s="7" t="inlineStr">
+      <c r="AU24" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AV24" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -11451,14 +11451,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AX24" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="AY24" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AX24" s="7" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="AY24" s="9" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AZ24" s="6" t="inlineStr">
@@ -11521,12 +11521,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BL24" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BM24" s="7" t="inlineStr">
+      <c r="BL24" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BM24" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -11541,9 +11541,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BP24" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
+      <c r="BP24" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
     </row>
@@ -11568,9 +11568,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E25" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="E25" s="9" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="F25" s="6" t="inlineStr">
@@ -11578,22 +11578,22 @@
           <t>API</t>
         </is>
       </c>
-      <c r="G25" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="H25" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="I25" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="J25" s="7" t="inlineStr">
+      <c r="G25" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="H25" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="I25" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="J25" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -11608,7 +11608,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="M25" s="7" t="inlineStr">
+      <c r="M25" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -11618,17 +11618,17 @@
           <t>API</t>
         </is>
       </c>
-      <c r="O25" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="P25" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Q25" s="7" t="inlineStr">
+      <c r="O25" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="P25" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Q25" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -11658,22 +11658,22 @@
           <t>API</t>
         </is>
       </c>
-      <c r="W25" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="X25" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Y25" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Z25" s="7" t="inlineStr">
+      <c r="W25" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="X25" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Y25" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Z25" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -11693,22 +11693,22 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AD25" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AE25" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AF25" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AG25" s="7" t="inlineStr">
+      <c r="AD25" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AE25" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AF25" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AG25" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -11718,7 +11718,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AI25" s="7" t="inlineStr">
+      <c r="AI25" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -11743,17 +11743,17 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AN25" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AO25" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AP25" s="7" t="inlineStr">
+      <c r="AN25" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AO25" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AP25" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -11768,7 +11768,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AS25" s="7" t="inlineStr">
+      <c r="AS25" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -11778,12 +11778,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AU25" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AV25" s="7" t="inlineStr">
+      <c r="AU25" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AV25" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -11793,14 +11793,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AX25" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="AY25" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AX25" s="7" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="AY25" s="9" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AZ25" s="6" t="inlineStr">
@@ -11863,12 +11863,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BL25" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BM25" s="7" t="inlineStr">
+      <c r="BL25" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BM25" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -11883,9 +11883,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BP25" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
+      <c r="BP25" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
     </row>
@@ -11910,9 +11910,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E26" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="E26" s="9" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="F26" s="6" t="inlineStr">
@@ -11920,22 +11920,22 @@
           <t>API</t>
         </is>
       </c>
-      <c r="G26" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="H26" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="I26" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="J26" s="7" t="inlineStr">
+      <c r="G26" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="H26" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="I26" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="J26" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -11950,7 +11950,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="M26" s="7" t="inlineStr">
+      <c r="M26" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -11960,17 +11960,17 @@
           <t>API</t>
         </is>
       </c>
-      <c r="O26" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="P26" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Q26" s="7" t="inlineStr">
+      <c r="O26" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="P26" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Q26" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -12000,22 +12000,22 @@
           <t>API</t>
         </is>
       </c>
-      <c r="W26" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="X26" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Y26" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Z26" s="7" t="inlineStr">
+      <c r="W26" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="X26" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Y26" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Z26" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -12035,22 +12035,22 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AD26" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AE26" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AF26" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AG26" s="7" t="inlineStr">
+      <c r="AD26" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AE26" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AF26" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AG26" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -12060,7 +12060,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AI26" s="7" t="inlineStr">
+      <c r="AI26" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -12085,17 +12085,17 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AN26" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AO26" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AP26" s="7" t="inlineStr">
+      <c r="AN26" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AO26" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AP26" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -12110,7 +12110,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AS26" s="7" t="inlineStr">
+      <c r="AS26" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -12120,12 +12120,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AU26" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AV26" s="7" t="inlineStr">
+      <c r="AU26" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AV26" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -12135,14 +12135,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AX26" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="AY26" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AX26" s="7" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="AY26" s="9" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AZ26" s="6" t="inlineStr">
@@ -12205,12 +12205,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BL26" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BM26" s="7" t="inlineStr">
+      <c r="BL26" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BM26" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -12225,9 +12225,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BP26" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
+      <c r="BP26" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
     </row>
@@ -12262,22 +12262,22 @@
           <t>API</t>
         </is>
       </c>
-      <c r="G27" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="H27" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="I27" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="J27" s="7" t="inlineStr">
+      <c r="G27" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="H27" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="I27" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="J27" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -12292,7 +12292,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="M27" s="7" t="inlineStr">
+      <c r="M27" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -12302,17 +12302,17 @@
           <t>API</t>
         </is>
       </c>
-      <c r="O27" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="P27" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Q27" s="7" t="inlineStr">
+      <c r="O27" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="P27" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Q27" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -12342,22 +12342,22 @@
           <t>API</t>
         </is>
       </c>
-      <c r="W27" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="X27" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Y27" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Z27" s="7" t="inlineStr">
+      <c r="W27" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="X27" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Y27" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Z27" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -12377,22 +12377,22 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AD27" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AE27" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AF27" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AG27" s="7" t="inlineStr">
+      <c r="AD27" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AE27" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AF27" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AG27" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -12402,7 +12402,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AI27" s="7" t="inlineStr">
+      <c r="AI27" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -12427,17 +12427,17 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AN27" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AO27" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AP27" s="7" t="inlineStr">
+      <c r="AN27" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AO27" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AP27" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -12452,7 +12452,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AS27" s="7" t="inlineStr">
+      <c r="AS27" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -12462,12 +12462,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AU27" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AV27" s="7" t="inlineStr">
+      <c r="AU27" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AV27" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -12477,7 +12477,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AX27" s="8" t="inlineStr">
+      <c r="AX27" s="7" t="inlineStr">
         <is>
           <t>AMBIGUOUS</t>
         </is>
@@ -12547,12 +12547,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BL27" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BM27" s="7" t="inlineStr">
+      <c r="BL27" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BM27" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -12588,7 +12588,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D4"/>
+  <dimension ref="A1:D21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -12622,7 +12622,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>STM32WL55CC</t>
+          <t>STM32WL54CC</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -12644,7 +12644,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>STM32WL55CC</t>
+          <t>STM32WL54CC</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -12666,20 +12666,394 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
+          <t>STM32WLE4C8</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Table 26. General operating conditions: V_DD min reads '1.8(1)' — the figure is qualified or corrupted by a footnote</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>STM32WLE5JB</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Table 26. General operating conditions: V_DD min reads '1.8(1)' — the figure is qualified or corrupted by a footnote</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>STM32WL54JC</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Core</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>cover names Arm Cortex-M4, Arm Cortex-M0+; ST reports the application core here and the others as co-processors</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>STM32WL54JC</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Table 26. General operating conditions: V_DD min reads '1.8(1)' — the figure is qualified or corrupted by a footnote</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>STM32WLE5CC</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Table 26. General operating conditions: V_DD min reads '1.8(1)' — the figure is qualified or corrupted by a footnote</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>STM32WLE5JC</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Table 26. General operating conditions: V_DD min reads '1.8(1)' — the figure is qualified or corrupted by a footnote</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>STM32WL55JC</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Core</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>cover names Arm Cortex-M4, Arm Cortex-M0+; ST reports the application core here and the others as co-processors</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>STM32WL55JC</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Table 26. General operating conditions: V_DD min reads '1.8(1)' — the figure is qualified or corrupted by a footnote</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>STM32WL55CC</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Core</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>cover names Arm Cortex-M4, Arm Cortex-M0+; ST reports the application core here and the others as co-processors</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>STM32WL55CC</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Table 26. General operating conditions: V_DD min reads '1.8(1)' — the figure is qualified or corrupted by a footnote</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>STM32WLE5J8</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Table 26. General operating conditions: V_DD min reads '1.8(1)' — the figure is qualified or corrupted by a footnote</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>STM32WLE4J8</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Table 26. General operating conditions: V_DD min reads '1.8(1)' — the figure is qualified or corrupted by a footnote</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>STM32WLE4JB</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Table 26. General operating conditions: V_DD min reads '1.8(1)' — the figure is qualified or corrupted by a footnote</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>STM32WLE4CB</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Table 26. General operating conditions: V_DD min reads '1.8(1)' — the figure is qualified or corrupted by a footnote</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>STM32WLE4CC</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Table 26. General operating conditions: V_DD min reads '1.8(1)' — the figure is qualified or corrupted by a footnote</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>STM32WLE4JC</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Table 26. General operating conditions: V_DD min reads '1.8(1)' — the figure is qualified or corrupted by a footnote</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>STM32WLE5CB</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Table 26. General operating conditions: V_DD min reads '1.8(1)' — the figure is qualified or corrupted by a footnote</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
           <t>STM32WLE5C8</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="B21" t="inlineStr">
         <is>
           <t>Supply Voltage (V) min</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="C21" t="inlineStr">
         <is>
           <t>AMBIGUOUS</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="D21" t="inlineStr">
         <is>
           <t>Table 26. General operating conditions: V_DD min reads '1.8(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>

--- a/product_selector_out/STM32WL5x-Ex.xlsx
+++ b/product_selector_out/STM32WL5x-Ex.xlsx
@@ -61,12 +61,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFEB9C"/>
+        <fgColor rgb="00F2F2F2"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00F2F2F2"/>
+        <fgColor rgb="00FFEB9C"/>
       </patternFill>
     </fill>
     <fill>
@@ -1350,7 +1350,7 @@
       </c>
       <c r="BP12" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32wl55cc.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -1692,7 +1692,7 @@
       </c>
       <c r="BP13" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32wle5c8.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -2034,7 +2034,7 @@
       </c>
       <c r="BP14" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32wle5c8.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -2376,7 +2376,7 @@
       </c>
       <c r="BP15" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32wl55cc.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -2718,7 +2718,7 @@
       </c>
       <c r="BP16" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32wle5c8.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -3060,7 +3060,7 @@
       </c>
       <c r="BP17" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32wle5c8.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -3402,7 +3402,7 @@
       </c>
       <c r="BP18" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32wl55cc.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -4086,7 +4086,7 @@
       </c>
       <c r="BP20" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32wle5c8.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -4428,7 +4428,7 @@
       </c>
       <c r="BP21" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32wle5c8.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -4770,7 +4770,7 @@
       </c>
       <c r="BP22" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32wle5c8.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -5112,7 +5112,7 @@
       </c>
       <c r="BP23" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32wle5c8.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -5454,7 +5454,7 @@
       </c>
       <c r="BP24" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32wle5c8.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -5796,7 +5796,7 @@
       </c>
       <c r="BP25" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32wle5c8.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -6138,7 +6138,7 @@
       </c>
       <c r="BP26" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32wle5c8.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -7122,9 +7122,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E12" s="7" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="E12" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F12" s="6" t="inlineStr">
@@ -7132,7 +7132,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="G12" s="8" t="inlineStr">
+      <c r="G12" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -7147,7 +7147,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="J12" s="8" t="inlineStr">
+      <c r="J12" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -7162,7 +7162,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="M12" s="8" t="inlineStr">
+      <c r="M12" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -7172,17 +7172,17 @@
           <t>API</t>
         </is>
       </c>
-      <c r="O12" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="P12" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Q12" s="8" t="inlineStr">
+      <c r="O12" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="P12" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Q12" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -7212,22 +7212,22 @@
           <t>API</t>
         </is>
       </c>
-      <c r="W12" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="X12" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Y12" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Z12" s="8" t="inlineStr">
+      <c r="W12" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="X12" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Y12" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Z12" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -7247,22 +7247,22 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AD12" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AE12" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AF12" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AG12" s="8" t="inlineStr">
+      <c r="AD12" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AE12" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AF12" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AG12" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -7272,7 +7272,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AI12" s="8" t="inlineStr">
+      <c r="AI12" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -7297,17 +7297,17 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AN12" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AO12" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AP12" s="8" t="inlineStr">
+      <c r="AN12" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AO12" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AP12" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -7322,7 +7322,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AS12" s="8" t="inlineStr">
+      <c r="AS12" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -7332,12 +7332,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AU12" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AV12" s="8" t="inlineStr">
+      <c r="AU12" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AV12" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -7347,14 +7347,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AX12" s="7" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AY12" s="9" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AX12" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AY12" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AZ12" s="6" t="inlineStr">
@@ -7417,12 +7417,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BL12" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BM12" s="8" t="inlineStr">
+      <c r="BL12" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BM12" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -7437,9 +7437,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BP12" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BP12" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -7464,9 +7464,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E13" s="9" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="E13" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F13" s="6" t="inlineStr">
@@ -7474,22 +7474,22 @@
           <t>API</t>
         </is>
       </c>
-      <c r="G13" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="H13" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="I13" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="J13" s="8" t="inlineStr">
+      <c r="G13" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="H13" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="I13" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="J13" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -7504,7 +7504,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="M13" s="8" t="inlineStr">
+      <c r="M13" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -7514,17 +7514,17 @@
           <t>API</t>
         </is>
       </c>
-      <c r="O13" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="P13" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Q13" s="8" t="inlineStr">
+      <c r="O13" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="P13" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Q13" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -7554,22 +7554,22 @@
           <t>API</t>
         </is>
       </c>
-      <c r="W13" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="X13" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Y13" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Z13" s="8" t="inlineStr">
+      <c r="W13" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="X13" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Y13" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Z13" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -7589,22 +7589,22 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AD13" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AE13" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AF13" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AG13" s="8" t="inlineStr">
+      <c r="AD13" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AE13" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AF13" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AG13" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -7614,7 +7614,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AI13" s="8" t="inlineStr">
+      <c r="AI13" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -7639,17 +7639,17 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AN13" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AO13" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AP13" s="8" t="inlineStr">
+      <c r="AN13" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AO13" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AP13" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -7664,7 +7664,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AS13" s="8" t="inlineStr">
+      <c r="AS13" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -7674,12 +7674,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AU13" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AV13" s="8" t="inlineStr">
+      <c r="AU13" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AV13" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -7689,14 +7689,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AX13" s="7" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AY13" s="9" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AX13" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AY13" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AZ13" s="6" t="inlineStr">
@@ -7759,12 +7759,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BL13" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BM13" s="8" t="inlineStr">
+      <c r="BL13" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BM13" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -7779,9 +7779,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BP13" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BP13" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -7806,9 +7806,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E14" s="9" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="E14" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F14" s="6" t="inlineStr">
@@ -7816,22 +7816,22 @@
           <t>API</t>
         </is>
       </c>
-      <c r="G14" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="H14" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="I14" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="J14" s="8" t="inlineStr">
+      <c r="G14" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="H14" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="I14" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="J14" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -7846,7 +7846,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="M14" s="8" t="inlineStr">
+      <c r="M14" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -7856,17 +7856,17 @@
           <t>API</t>
         </is>
       </c>
-      <c r="O14" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="P14" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Q14" s="8" t="inlineStr">
+      <c r="O14" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="P14" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Q14" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -7896,22 +7896,22 @@
           <t>API</t>
         </is>
       </c>
-      <c r="W14" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="X14" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Y14" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Z14" s="8" t="inlineStr">
+      <c r="W14" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="X14" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Y14" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Z14" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -7931,22 +7931,22 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AD14" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AE14" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AF14" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AG14" s="8" t="inlineStr">
+      <c r="AD14" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AE14" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AF14" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AG14" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -7956,7 +7956,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AI14" s="8" t="inlineStr">
+      <c r="AI14" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -7981,17 +7981,17 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AN14" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AO14" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AP14" s="8" t="inlineStr">
+      <c r="AN14" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AO14" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AP14" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -8006,7 +8006,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AS14" s="8" t="inlineStr">
+      <c r="AS14" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -8016,12 +8016,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AU14" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AV14" s="8" t="inlineStr">
+      <c r="AU14" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AV14" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -8031,14 +8031,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AX14" s="7" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AY14" s="9" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AX14" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AY14" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AZ14" s="6" t="inlineStr">
@@ -8101,12 +8101,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BL14" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BM14" s="8" t="inlineStr">
+      <c r="BL14" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BM14" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -8121,9 +8121,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BP14" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BP14" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -8148,9 +8148,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E15" s="7" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="E15" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F15" s="6" t="inlineStr">
@@ -8158,7 +8158,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="G15" s="8" t="inlineStr">
+      <c r="G15" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -8173,7 +8173,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="J15" s="8" t="inlineStr">
+      <c r="J15" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -8188,7 +8188,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="M15" s="8" t="inlineStr">
+      <c r="M15" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -8198,17 +8198,17 @@
           <t>API</t>
         </is>
       </c>
-      <c r="O15" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="P15" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Q15" s="8" t="inlineStr">
+      <c r="O15" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="P15" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Q15" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -8238,22 +8238,22 @@
           <t>API</t>
         </is>
       </c>
-      <c r="W15" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="X15" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Y15" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Z15" s="8" t="inlineStr">
+      <c r="W15" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="X15" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Y15" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Z15" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -8273,22 +8273,22 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AD15" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AE15" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AF15" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AG15" s="8" t="inlineStr">
+      <c r="AD15" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AE15" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AF15" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AG15" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -8298,7 +8298,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AI15" s="8" t="inlineStr">
+      <c r="AI15" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -8323,17 +8323,17 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AN15" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AO15" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AP15" s="8" t="inlineStr">
+      <c r="AN15" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AO15" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AP15" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -8348,7 +8348,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AS15" s="8" t="inlineStr">
+      <c r="AS15" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -8358,12 +8358,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AU15" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AV15" s="8" t="inlineStr">
+      <c r="AU15" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AV15" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -8373,14 +8373,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AX15" s="7" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AY15" s="9" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AX15" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AY15" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AZ15" s="6" t="inlineStr">
@@ -8443,12 +8443,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BL15" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BM15" s="8" t="inlineStr">
+      <c r="BL15" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BM15" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -8463,9 +8463,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BP15" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BP15" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -8490,9 +8490,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E16" s="9" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="E16" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F16" s="6" t="inlineStr">
@@ -8500,22 +8500,22 @@
           <t>API</t>
         </is>
       </c>
-      <c r="G16" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="H16" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="I16" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="J16" s="8" t="inlineStr">
+      <c r="G16" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="H16" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="I16" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="J16" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -8530,7 +8530,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="M16" s="8" t="inlineStr">
+      <c r="M16" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -8540,17 +8540,17 @@
           <t>API</t>
         </is>
       </c>
-      <c r="O16" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="P16" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Q16" s="8" t="inlineStr">
+      <c r="O16" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="P16" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Q16" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -8580,22 +8580,22 @@
           <t>API</t>
         </is>
       </c>
-      <c r="W16" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="X16" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Y16" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Z16" s="8" t="inlineStr">
+      <c r="W16" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="X16" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Y16" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Z16" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -8615,22 +8615,22 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AD16" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AE16" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AF16" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AG16" s="8" t="inlineStr">
+      <c r="AD16" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AE16" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AF16" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AG16" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -8640,7 +8640,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AI16" s="8" t="inlineStr">
+      <c r="AI16" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -8665,17 +8665,17 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AN16" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AO16" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AP16" s="8" t="inlineStr">
+      <c r="AN16" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AO16" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AP16" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -8690,7 +8690,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AS16" s="8" t="inlineStr">
+      <c r="AS16" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -8700,12 +8700,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AU16" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AV16" s="8" t="inlineStr">
+      <c r="AU16" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AV16" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -8715,14 +8715,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AX16" s="7" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AY16" s="9" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AX16" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AY16" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AZ16" s="6" t="inlineStr">
@@ -8785,12 +8785,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BL16" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BM16" s="8" t="inlineStr">
+      <c r="BL16" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BM16" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -8805,9 +8805,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BP16" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BP16" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -8832,9 +8832,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E17" s="9" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="E17" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F17" s="6" t="inlineStr">
@@ -8842,22 +8842,22 @@
           <t>API</t>
         </is>
       </c>
-      <c r="G17" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="H17" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="I17" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="J17" s="8" t="inlineStr">
+      <c r="G17" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="H17" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="I17" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="J17" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -8872,7 +8872,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="M17" s="8" t="inlineStr">
+      <c r="M17" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -8882,17 +8882,17 @@
           <t>API</t>
         </is>
       </c>
-      <c r="O17" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="P17" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Q17" s="8" t="inlineStr">
+      <c r="O17" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="P17" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Q17" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -8922,22 +8922,22 @@
           <t>API</t>
         </is>
       </c>
-      <c r="W17" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="X17" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Y17" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Z17" s="8" t="inlineStr">
+      <c r="W17" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="X17" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Y17" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Z17" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -8957,22 +8957,22 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AD17" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AE17" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AF17" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AG17" s="8" t="inlineStr">
+      <c r="AD17" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AE17" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AF17" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AG17" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -8982,7 +8982,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AI17" s="8" t="inlineStr">
+      <c r="AI17" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -9007,17 +9007,17 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AN17" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AO17" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AP17" s="8" t="inlineStr">
+      <c r="AN17" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AO17" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AP17" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -9032,7 +9032,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AS17" s="8" t="inlineStr">
+      <c r="AS17" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -9042,12 +9042,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AU17" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AV17" s="8" t="inlineStr">
+      <c r="AU17" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AV17" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -9057,14 +9057,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AX17" s="7" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AY17" s="9" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AX17" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AY17" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AZ17" s="6" t="inlineStr">
@@ -9127,12 +9127,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BL17" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BM17" s="8" t="inlineStr">
+      <c r="BL17" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BM17" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -9147,9 +9147,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BP17" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BP17" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -9174,9 +9174,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E18" s="7" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="E18" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F18" s="6" t="inlineStr">
@@ -9184,7 +9184,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="G18" s="8" t="inlineStr">
+      <c r="G18" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -9199,7 +9199,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="J18" s="8" t="inlineStr">
+      <c r="J18" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -9214,7 +9214,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="M18" s="8" t="inlineStr">
+      <c r="M18" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -9224,17 +9224,17 @@
           <t>API</t>
         </is>
       </c>
-      <c r="O18" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="P18" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Q18" s="8" t="inlineStr">
+      <c r="O18" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="P18" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Q18" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -9264,22 +9264,22 @@
           <t>API</t>
         </is>
       </c>
-      <c r="W18" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="X18" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Y18" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Z18" s="8" t="inlineStr">
+      <c r="W18" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="X18" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Y18" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Z18" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -9299,22 +9299,22 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AD18" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AE18" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AF18" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AG18" s="8" t="inlineStr">
+      <c r="AD18" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AE18" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AF18" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AG18" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -9324,7 +9324,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AI18" s="8" t="inlineStr">
+      <c r="AI18" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -9349,17 +9349,17 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AN18" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AO18" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AP18" s="8" t="inlineStr">
+      <c r="AN18" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AO18" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AP18" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -9374,7 +9374,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AS18" s="8" t="inlineStr">
+      <c r="AS18" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -9384,12 +9384,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AU18" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AV18" s="8" t="inlineStr">
+      <c r="AU18" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AV18" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -9399,14 +9399,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AX18" s="7" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AY18" s="9" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AX18" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AY18" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AZ18" s="6" t="inlineStr">
@@ -9469,12 +9469,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BL18" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BM18" s="8" t="inlineStr">
+      <c r="BL18" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BM18" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -9489,9 +9489,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BP18" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BP18" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -9516,7 +9516,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E19" s="7" t="inlineStr">
+      <c r="E19" s="8" t="inlineStr">
         <is>
           <t>AMBIGUOUS</t>
         </is>
@@ -9526,7 +9526,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="G19" s="8" t="inlineStr">
+      <c r="G19" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -9541,7 +9541,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="J19" s="8" t="inlineStr">
+      <c r="J19" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -9556,7 +9556,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="M19" s="8" t="inlineStr">
+      <c r="M19" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -9566,17 +9566,17 @@
           <t>API</t>
         </is>
       </c>
-      <c r="O19" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="P19" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Q19" s="8" t="inlineStr">
+      <c r="O19" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="P19" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Q19" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -9606,22 +9606,22 @@
           <t>API</t>
         </is>
       </c>
-      <c r="W19" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="X19" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Y19" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Z19" s="8" t="inlineStr">
+      <c r="W19" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="X19" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Y19" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Z19" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -9641,22 +9641,22 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AD19" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AE19" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AF19" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AG19" s="8" t="inlineStr">
+      <c r="AD19" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AE19" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AF19" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AG19" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -9666,7 +9666,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AI19" s="8" t="inlineStr">
+      <c r="AI19" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -9691,17 +9691,17 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AN19" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AO19" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AP19" s="8" t="inlineStr">
+      <c r="AN19" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AO19" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AP19" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -9716,7 +9716,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AS19" s="8" t="inlineStr">
+      <c r="AS19" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -9726,12 +9726,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AU19" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AV19" s="8" t="inlineStr">
+      <c r="AU19" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AV19" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -9741,7 +9741,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AX19" s="7" t="inlineStr">
+      <c r="AX19" s="8" t="inlineStr">
         <is>
           <t>AMBIGUOUS</t>
         </is>
@@ -9811,12 +9811,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BL19" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BM19" s="8" t="inlineStr">
+      <c r="BL19" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BM19" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -9858,9 +9858,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E20" s="9" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="E20" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F20" s="6" t="inlineStr">
@@ -9868,22 +9868,22 @@
           <t>API</t>
         </is>
       </c>
-      <c r="G20" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="H20" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="I20" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="J20" s="8" t="inlineStr">
+      <c r="G20" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="H20" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="I20" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="J20" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -9898,7 +9898,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="M20" s="8" t="inlineStr">
+      <c r="M20" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -9908,17 +9908,17 @@
           <t>API</t>
         </is>
       </c>
-      <c r="O20" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="P20" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Q20" s="8" t="inlineStr">
+      <c r="O20" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="P20" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Q20" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -9948,22 +9948,22 @@
           <t>API</t>
         </is>
       </c>
-      <c r="W20" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="X20" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Y20" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Z20" s="8" t="inlineStr">
+      <c r="W20" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="X20" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Y20" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Z20" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -9983,22 +9983,22 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AD20" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AE20" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AF20" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AG20" s="8" t="inlineStr">
+      <c r="AD20" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AE20" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AF20" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AG20" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -10008,7 +10008,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AI20" s="8" t="inlineStr">
+      <c r="AI20" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -10033,17 +10033,17 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AN20" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AO20" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AP20" s="8" t="inlineStr">
+      <c r="AN20" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AO20" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AP20" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -10058,7 +10058,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AS20" s="8" t="inlineStr">
+      <c r="AS20" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -10068,12 +10068,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AU20" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AV20" s="8" t="inlineStr">
+      <c r="AU20" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AV20" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -10083,14 +10083,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AX20" s="7" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AY20" s="9" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AX20" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AY20" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AZ20" s="6" t="inlineStr">
@@ -10153,12 +10153,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BL20" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BM20" s="8" t="inlineStr">
+      <c r="BL20" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BM20" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -10173,9 +10173,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BP20" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BP20" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -10200,9 +10200,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E21" s="9" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="E21" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F21" s="6" t="inlineStr">
@@ -10210,22 +10210,22 @@
           <t>API</t>
         </is>
       </c>
-      <c r="G21" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="H21" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="I21" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="J21" s="8" t="inlineStr">
+      <c r="G21" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="H21" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="I21" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="J21" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -10240,7 +10240,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="M21" s="8" t="inlineStr">
+      <c r="M21" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -10250,17 +10250,17 @@
           <t>API</t>
         </is>
       </c>
-      <c r="O21" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="P21" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Q21" s="8" t="inlineStr">
+      <c r="O21" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="P21" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Q21" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -10290,22 +10290,22 @@
           <t>API</t>
         </is>
       </c>
-      <c r="W21" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="X21" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Y21" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Z21" s="8" t="inlineStr">
+      <c r="W21" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="X21" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Y21" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Z21" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -10325,22 +10325,22 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AD21" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AE21" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AF21" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AG21" s="8" t="inlineStr">
+      <c r="AD21" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AE21" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AF21" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AG21" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -10350,7 +10350,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AI21" s="8" t="inlineStr">
+      <c r="AI21" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -10375,17 +10375,17 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AN21" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AO21" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AP21" s="8" t="inlineStr">
+      <c r="AN21" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AO21" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AP21" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -10400,7 +10400,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AS21" s="8" t="inlineStr">
+      <c r="AS21" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -10410,12 +10410,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AU21" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AV21" s="8" t="inlineStr">
+      <c r="AU21" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AV21" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -10425,14 +10425,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AX21" s="7" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AY21" s="9" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AX21" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AY21" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AZ21" s="6" t="inlineStr">
@@ -10495,12 +10495,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BL21" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BM21" s="8" t="inlineStr">
+      <c r="BL21" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BM21" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -10515,9 +10515,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BP21" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BP21" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -10542,9 +10542,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E22" s="9" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="E22" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F22" s="6" t="inlineStr">
@@ -10552,22 +10552,22 @@
           <t>API</t>
         </is>
       </c>
-      <c r="G22" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="H22" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="I22" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="J22" s="8" t="inlineStr">
+      <c r="G22" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="H22" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="I22" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="J22" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -10582,7 +10582,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="M22" s="8" t="inlineStr">
+      <c r="M22" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -10592,17 +10592,17 @@
           <t>API</t>
         </is>
       </c>
-      <c r="O22" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="P22" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Q22" s="8" t="inlineStr">
+      <c r="O22" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="P22" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Q22" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -10632,22 +10632,22 @@
           <t>API</t>
         </is>
       </c>
-      <c r="W22" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="X22" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Y22" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Z22" s="8" t="inlineStr">
+      <c r="W22" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="X22" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Y22" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Z22" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -10667,22 +10667,22 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AD22" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AE22" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AF22" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AG22" s="8" t="inlineStr">
+      <c r="AD22" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AE22" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AF22" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AG22" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -10692,7 +10692,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AI22" s="8" t="inlineStr">
+      <c r="AI22" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -10717,17 +10717,17 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AN22" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AO22" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AP22" s="8" t="inlineStr">
+      <c r="AN22" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AO22" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AP22" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -10742,7 +10742,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AS22" s="8" t="inlineStr">
+      <c r="AS22" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -10752,12 +10752,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AU22" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AV22" s="8" t="inlineStr">
+      <c r="AU22" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AV22" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -10767,14 +10767,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AX22" s="7" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AY22" s="9" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AX22" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AY22" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AZ22" s="6" t="inlineStr">
@@ -10837,12 +10837,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BL22" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BM22" s="8" t="inlineStr">
+      <c r="BL22" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BM22" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -10857,9 +10857,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BP22" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BP22" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -10884,9 +10884,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E23" s="9" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="E23" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F23" s="6" t="inlineStr">
@@ -10894,22 +10894,22 @@
           <t>API</t>
         </is>
       </c>
-      <c r="G23" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="H23" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="I23" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="J23" s="8" t="inlineStr">
+      <c r="G23" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="H23" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="I23" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="J23" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -10924,7 +10924,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="M23" s="8" t="inlineStr">
+      <c r="M23" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -10934,17 +10934,17 @@
           <t>API</t>
         </is>
       </c>
-      <c r="O23" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="P23" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Q23" s="8" t="inlineStr">
+      <c r="O23" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="P23" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Q23" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -10974,22 +10974,22 @@
           <t>API</t>
         </is>
       </c>
-      <c r="W23" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="X23" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Y23" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Z23" s="8" t="inlineStr">
+      <c r="W23" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="X23" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Y23" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Z23" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -11009,22 +11009,22 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AD23" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AE23" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AF23" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AG23" s="8" t="inlineStr">
+      <c r="AD23" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AE23" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AF23" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AG23" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -11034,7 +11034,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AI23" s="8" t="inlineStr">
+      <c r="AI23" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -11059,17 +11059,17 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AN23" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AO23" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AP23" s="8" t="inlineStr">
+      <c r="AN23" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AO23" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AP23" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -11084,7 +11084,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AS23" s="8" t="inlineStr">
+      <c r="AS23" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -11094,12 +11094,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AU23" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AV23" s="8" t="inlineStr">
+      <c r="AU23" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AV23" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -11109,14 +11109,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AX23" s="7" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AY23" s="9" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AX23" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AY23" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AZ23" s="6" t="inlineStr">
@@ -11179,12 +11179,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BL23" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BM23" s="8" t="inlineStr">
+      <c r="BL23" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BM23" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -11199,9 +11199,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BP23" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BP23" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -11226,9 +11226,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E24" s="9" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="E24" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F24" s="6" t="inlineStr">
@@ -11236,22 +11236,22 @@
           <t>API</t>
         </is>
       </c>
-      <c r="G24" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="H24" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="I24" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="J24" s="8" t="inlineStr">
+      <c r="G24" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="H24" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="I24" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="J24" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -11266,7 +11266,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="M24" s="8" t="inlineStr">
+      <c r="M24" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -11276,17 +11276,17 @@
           <t>API</t>
         </is>
       </c>
-      <c r="O24" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="P24" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Q24" s="8" t="inlineStr">
+      <c r="O24" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="P24" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Q24" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -11316,22 +11316,22 @@
           <t>API</t>
         </is>
       </c>
-      <c r="W24" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="X24" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Y24" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Z24" s="8" t="inlineStr">
+      <c r="W24" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="X24" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Y24" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Z24" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -11351,22 +11351,22 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AD24" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AE24" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AF24" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AG24" s="8" t="inlineStr">
+      <c r="AD24" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AE24" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AF24" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AG24" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -11376,7 +11376,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AI24" s="8" t="inlineStr">
+      <c r="AI24" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -11401,17 +11401,17 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AN24" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AO24" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AP24" s="8" t="inlineStr">
+      <c r="AN24" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AO24" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AP24" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -11426,7 +11426,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AS24" s="8" t="inlineStr">
+      <c r="AS24" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -11436,12 +11436,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AU24" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AV24" s="8" t="inlineStr">
+      <c r="AU24" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AV24" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -11451,14 +11451,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AX24" s="7" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AY24" s="9" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AX24" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AY24" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AZ24" s="6" t="inlineStr">
@@ -11521,12 +11521,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BL24" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BM24" s="8" t="inlineStr">
+      <c r="BL24" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BM24" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -11541,9 +11541,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BP24" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BP24" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -11568,9 +11568,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E25" s="9" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="E25" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F25" s="6" t="inlineStr">
@@ -11578,22 +11578,22 @@
           <t>API</t>
         </is>
       </c>
-      <c r="G25" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="H25" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="I25" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="J25" s="8" t="inlineStr">
+      <c r="G25" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="H25" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="I25" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="J25" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -11608,7 +11608,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="M25" s="8" t="inlineStr">
+      <c r="M25" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -11618,17 +11618,17 @@
           <t>API</t>
         </is>
       </c>
-      <c r="O25" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="P25" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Q25" s="8" t="inlineStr">
+      <c r="O25" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="P25" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Q25" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -11658,22 +11658,22 @@
           <t>API</t>
         </is>
       </c>
-      <c r="W25" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="X25" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Y25" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Z25" s="8" t="inlineStr">
+      <c r="W25" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="X25" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Y25" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Z25" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -11693,22 +11693,22 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AD25" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AE25" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AF25" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AG25" s="8" t="inlineStr">
+      <c r="AD25" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AE25" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AF25" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AG25" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -11718,7 +11718,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AI25" s="8" t="inlineStr">
+      <c r="AI25" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -11743,17 +11743,17 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AN25" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AO25" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AP25" s="8" t="inlineStr">
+      <c r="AN25" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AO25" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AP25" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -11768,7 +11768,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AS25" s="8" t="inlineStr">
+      <c r="AS25" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -11778,12 +11778,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AU25" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AV25" s="8" t="inlineStr">
+      <c r="AU25" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AV25" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -11793,14 +11793,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AX25" s="7" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AY25" s="9" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AX25" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AY25" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AZ25" s="6" t="inlineStr">
@@ -11863,12 +11863,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BL25" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BM25" s="8" t="inlineStr">
+      <c r="BL25" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BM25" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -11883,9 +11883,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BP25" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BP25" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -11910,9 +11910,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E26" s="9" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="E26" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F26" s="6" t="inlineStr">
@@ -11920,22 +11920,22 @@
           <t>API</t>
         </is>
       </c>
-      <c r="G26" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="H26" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="I26" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="J26" s="8" t="inlineStr">
+      <c r="G26" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="H26" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="I26" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="J26" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -11950,7 +11950,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="M26" s="8" t="inlineStr">
+      <c r="M26" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -11960,17 +11960,17 @@
           <t>API</t>
         </is>
       </c>
-      <c r="O26" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="P26" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Q26" s="8" t="inlineStr">
+      <c r="O26" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="P26" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Q26" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -12000,22 +12000,22 @@
           <t>API</t>
         </is>
       </c>
-      <c r="W26" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="X26" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Y26" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Z26" s="8" t="inlineStr">
+      <c r="W26" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="X26" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Y26" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Z26" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -12035,22 +12035,22 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AD26" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AE26" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AF26" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AG26" s="8" t="inlineStr">
+      <c r="AD26" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AE26" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AF26" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AG26" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -12060,7 +12060,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AI26" s="8" t="inlineStr">
+      <c r="AI26" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -12085,17 +12085,17 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AN26" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AO26" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AP26" s="8" t="inlineStr">
+      <c r="AN26" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AO26" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AP26" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -12110,7 +12110,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AS26" s="8" t="inlineStr">
+      <c r="AS26" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -12120,12 +12120,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AU26" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AV26" s="8" t="inlineStr">
+      <c r="AU26" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AV26" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -12135,14 +12135,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AX26" s="7" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AY26" s="9" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AX26" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AY26" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AZ26" s="6" t="inlineStr">
@@ -12205,12 +12205,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BL26" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BM26" s="8" t="inlineStr">
+      <c r="BL26" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BM26" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -12225,9 +12225,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BP26" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BP26" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -12262,22 +12262,22 @@
           <t>API</t>
         </is>
       </c>
-      <c r="G27" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="H27" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="I27" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="J27" s="8" t="inlineStr">
+      <c r="G27" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="H27" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="I27" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="J27" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -12292,7 +12292,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="M27" s="8" t="inlineStr">
+      <c r="M27" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -12302,17 +12302,17 @@
           <t>API</t>
         </is>
       </c>
-      <c r="O27" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="P27" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Q27" s="8" t="inlineStr">
+      <c r="O27" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="P27" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Q27" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -12342,22 +12342,22 @@
           <t>API</t>
         </is>
       </c>
-      <c r="W27" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="X27" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Y27" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Z27" s="8" t="inlineStr">
+      <c r="W27" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="X27" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Y27" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Z27" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -12377,22 +12377,22 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AD27" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AE27" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AF27" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AG27" s="8" t="inlineStr">
+      <c r="AD27" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AE27" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AF27" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AG27" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -12402,7 +12402,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AI27" s="8" t="inlineStr">
+      <c r="AI27" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -12427,17 +12427,17 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AN27" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AO27" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AP27" s="8" t="inlineStr">
+      <c r="AN27" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AO27" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AP27" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -12452,7 +12452,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AS27" s="8" t="inlineStr">
+      <c r="AS27" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -12462,12 +12462,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AU27" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AV27" s="8" t="inlineStr">
+      <c r="AU27" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AV27" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -12477,7 +12477,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AX27" s="7" t="inlineStr">
+      <c r="AX27" s="8" t="inlineStr">
         <is>
           <t>AMBIGUOUS</t>
         </is>
@@ -12547,12 +12547,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BL27" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BM27" s="8" t="inlineStr">
+      <c r="BL27" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BM27" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -12588,7 +12588,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D21"/>
+  <dimension ref="A1:D4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -12622,7 +12622,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>STM32WL54CC</t>
+          <t>STM32WL55CC</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -12644,7 +12644,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>STM32WL54CC</t>
+          <t>STM32WL55CC</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -12666,7 +12666,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>STM32WLE4C8</t>
+          <t>STM32WLE5C8</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -12680,380 +12680,6 @@
         </is>
       </c>
       <c r="D4" t="inlineStr">
-        <is>
-          <t>Table 26. General operating conditions: V_DD min reads '1.8(1)' — the figure is qualified or corrupted by a footnote</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>STM32WLE5JB</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Supply Voltage (V) min</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>Table 26. General operating conditions: V_DD min reads '1.8(1)' — the figure is qualified or corrupted by a footnote</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>STM32WL54JC</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Core</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>cover names Arm Cortex-M4, Arm Cortex-M0+; ST reports the application core here and the others as co-processors</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>STM32WL54JC</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>Supply Voltage (V) min</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>Table 26. General operating conditions: V_DD min reads '1.8(1)' — the figure is qualified or corrupted by a footnote</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>STM32WLE5CC</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>Supply Voltage (V) min</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>Table 26. General operating conditions: V_DD min reads '1.8(1)' — the figure is qualified or corrupted by a footnote</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>STM32WLE5JC</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>Supply Voltage (V) min</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>Table 26. General operating conditions: V_DD min reads '1.8(1)' — the figure is qualified or corrupted by a footnote</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>STM32WL55JC</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>Core</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>cover names Arm Cortex-M4, Arm Cortex-M0+; ST reports the application core here and the others as co-processors</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>STM32WL55JC</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>Supply Voltage (V) min</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>Table 26. General operating conditions: V_DD min reads '1.8(1)' — the figure is qualified or corrupted by a footnote</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>STM32WL55CC</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>Core</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>cover names Arm Cortex-M4, Arm Cortex-M0+; ST reports the application core here and the others as co-processors</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>STM32WL55CC</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>Supply Voltage (V) min</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>Table 26. General operating conditions: V_DD min reads '1.8(1)' — the figure is qualified or corrupted by a footnote</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>STM32WLE5J8</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>Supply Voltage (V) min</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>Table 26. General operating conditions: V_DD min reads '1.8(1)' — the figure is qualified or corrupted by a footnote</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>STM32WLE4J8</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>Supply Voltage (V) min</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>Table 26. General operating conditions: V_DD min reads '1.8(1)' — the figure is qualified or corrupted by a footnote</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>STM32WLE4JB</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>Supply Voltage (V) min</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>Table 26. General operating conditions: V_DD min reads '1.8(1)' — the figure is qualified or corrupted by a footnote</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>STM32WLE4CB</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>Supply Voltage (V) min</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>Table 26. General operating conditions: V_DD min reads '1.8(1)' — the figure is qualified or corrupted by a footnote</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>STM32WLE4CC</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>Supply Voltage (V) min</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>Table 26. General operating conditions: V_DD min reads '1.8(1)' — the figure is qualified or corrupted by a footnote</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>STM32WLE4JC</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>Supply Voltage (V) min</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>Table 26. General operating conditions: V_DD min reads '1.8(1)' — the figure is qualified or corrupted by a footnote</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>STM32WLE5CB</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>Supply Voltage (V) min</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>Table 26. General operating conditions: V_DD min reads '1.8(1)' — the figure is qualified or corrupted by a footnote</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>STM32WLE5C8</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>Supply Voltage (V) min</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
         <is>
           <t>Table 26. General operating conditions: V_DD min reads '1.8(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>

--- a/product_selector_out/STM32WL5x-Ex.xlsx
+++ b/product_selector_out/STM32WL5x-Ex.xlsx
@@ -500,7 +500,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BP27"/>
+  <dimension ref="A1:BQ27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12.9375" customWidth="1" min="1" max="1"/>
@@ -570,7 +570,8 @@
     <col width="21.984375" customWidth="1" min="65" max="65"/>
     <col width="18" customWidth="1" min="66" max="66"/>
     <col width="18" customWidth="1" min="67" max="67"/>
-    <col width="52" customWidth="1" min="68" max="68"/>
+    <col width="18" customWidth="1" min="68" max="68"/>
+    <col width="52" customWidth="1" min="69" max="69"/>
   </cols>
   <sheetData>
     <row r="1"/>
@@ -913,6 +914,11 @@
         </is>
       </c>
       <c r="BP10" s="2" t="inlineStr">
+        <is>
+          <t>LPUART typ</t>
+        </is>
+      </c>
+      <c r="BQ10" s="2" t="inlineStr">
         <is>
           <t>Datasheet URL</t>
         </is>
@@ -1011,6 +1017,7 @@
       <c r="BN11" s="2" t="n"/>
       <c r="BO11" s="2" t="n"/>
       <c r="BP11" s="2" t="n"/>
+      <c r="BQ11" s="2" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
@@ -1353,6 +1360,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="BQ12" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
@@ -1695,6 +1707,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="BQ13" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
@@ -2037,6 +2054,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="BQ14" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
@@ -2379,6 +2401,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="BQ15" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="inlineStr">
@@ -2721,6 +2748,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="BQ16" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
@@ -3063,6 +3095,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="BQ17" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="3" t="inlineStr">
@@ -3405,6 +3442,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="BQ18" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
@@ -3744,6 +3786,11 @@
       </c>
       <c r="BP19" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BQ19" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32wl55cc.pdf</t>
         </is>
       </c>
@@ -4089,6 +4136,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="BQ20" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
@@ -4431,6 +4483,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="BQ21" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="3" t="inlineStr">
@@ -4773,6 +4830,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="BQ22" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="inlineStr">
@@ -5115,6 +5177,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="BQ23" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="3" t="inlineStr">
@@ -5457,6 +5524,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="BQ24" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="3" t="inlineStr">
@@ -5799,6 +5871,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="BQ25" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="3" t="inlineStr">
@@ -6141,6 +6218,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="BQ26" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="3" t="inlineStr">
@@ -6480,12 +6562,17 @@
       </c>
       <c r="BP27" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BQ27" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32wle5c8.pdf</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="67">
+  <mergeCells count="68">
     <mergeCell ref="P10:P11"/>
     <mergeCell ref="AS10:AS11"/>
     <mergeCell ref="AD10:AD11"/>
@@ -6508,14 +6595,13 @@
     <mergeCell ref="Q10:Q11"/>
     <mergeCell ref="AR10:AR11"/>
     <mergeCell ref="AT10:AT11"/>
-    <mergeCell ref="A9:BP9"/>
+    <mergeCell ref="A1:BQ8"/>
     <mergeCell ref="S10:S11"/>
-    <mergeCell ref="A1:BP8"/>
     <mergeCell ref="AV10:AV11"/>
     <mergeCell ref="BB10:BB11"/>
     <mergeCell ref="BI10:BI11"/>
+    <mergeCell ref="BM10:BM11"/>
     <mergeCell ref="BD10:BD11"/>
-    <mergeCell ref="BM10:BM11"/>
     <mergeCell ref="Y10:Z10"/>
     <mergeCell ref="AC10:AC11"/>
     <mergeCell ref="B10:B11"/>
@@ -6533,6 +6619,7 @@
     <mergeCell ref="BP10:BP11"/>
     <mergeCell ref="BK10:BK11"/>
     <mergeCell ref="A10:A11"/>
+    <mergeCell ref="A9:BQ9"/>
     <mergeCell ref="I10:I11"/>
     <mergeCell ref="AL10:AL11"/>
     <mergeCell ref="K10:K11"/>
@@ -6545,6 +6632,7 @@
     <mergeCell ref="AX10:AX11"/>
     <mergeCell ref="AZ10:AZ11"/>
     <mergeCell ref="BF10:BF11"/>
+    <mergeCell ref="BQ10:BQ11"/>
     <mergeCell ref="R10:R11"/>
     <mergeCell ref="U10:V10"/>
     <mergeCell ref="BO10:BO11"/>
@@ -6583,7 +6671,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BP27"/>
+  <dimension ref="A1:BQ27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -6654,6 +6742,7 @@
     <col width="16" customWidth="1" min="66" max="66"/>
     <col width="16" customWidth="1" min="67" max="67"/>
     <col width="16" customWidth="1" min="68" max="68"/>
+    <col width="16" customWidth="1" min="69" max="69"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -7002,6 +7091,11 @@
         </is>
       </c>
       <c r="BP10" s="2" t="inlineStr">
+        <is>
+          <t>LPUART typ</t>
+        </is>
+      </c>
+      <c r="BQ10" s="2" t="inlineStr">
         <is>
           <t>Datasheet URL</t>
         </is>
@@ -7100,6 +7194,7 @@
       <c r="BN11" s="2" t="n"/>
       <c r="BO11" s="2" t="n"/>
       <c r="BP11" s="2" t="n"/>
+      <c r="BQ11" s="2" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="6" t="inlineStr">
@@ -7442,6 +7537,11 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
+      <c r="BQ12" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="6" t="inlineStr">
@@ -7784,6 +7884,11 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
+      <c r="BQ13" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="6" t="inlineStr">
@@ -8126,6 +8231,11 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
+      <c r="BQ14" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="6" t="inlineStr">
@@ -8468,6 +8578,11 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
+      <c r="BQ15" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="6" t="inlineStr">
@@ -8810,6 +8925,11 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
+      <c r="BQ16" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="6" t="inlineStr">
@@ -9152,6 +9272,11 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
+      <c r="BQ17" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="6" t="inlineStr">
@@ -9494,6 +9619,11 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
+      <c r="BQ18" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="6" t="inlineStr">
@@ -9831,7 +9961,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BP19" s="6" t="inlineStr">
+      <c r="BP19" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BQ19" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -10178,6 +10313,11 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
+      <c r="BQ20" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="6" t="inlineStr">
@@ -10520,6 +10660,11 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
+      <c r="BQ21" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="6" t="inlineStr">
@@ -10862,6 +11007,11 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
+      <c r="BQ22" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="6" t="inlineStr">
@@ -11204,6 +11354,11 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
+      <c r="BQ23" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="6" t="inlineStr">
@@ -11546,6 +11701,11 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
+      <c r="BQ24" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="6" t="inlineStr">
@@ -11888,6 +12048,11 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
+      <c r="BQ25" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="6" t="inlineStr">
@@ -12230,6 +12395,11 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
+      <c r="BQ26" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="6" t="inlineStr">
@@ -12567,7 +12737,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BP27" s="6" t="inlineStr">
+      <c r="BP27" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BQ27" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -12575,8 +12750,8 @@
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A1:BP8"/>
-    <mergeCell ref="A9:BP9"/>
+    <mergeCell ref="A1:BQ8"/>
+    <mergeCell ref="A9:BQ9"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
